--- a/신고제도_행정사인터뷰/output/261014_입법영향분석_신고제도_행정사인터뷰_법령개정_필요사항.xlsx
+++ b/신고제도_행정사인터뷰/output/261014_입법영향분석_신고제도_행정사인터뷰_법령개정_필요사항.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -541,30 +541,73 @@
 [문제점] ① 법령은 옥외영업을 '영업장 면적 변경신고'로 설계해 즉시 처리·3일 내 수리 통지·미통지 시 간주, 시설 확인은 신고증 발급 후 사후 조사로 정했는데, 실무는 사전 협의→현장 방문→다른 기관 협의 뒤 수리 여부를 정하고 '보류' 상태로 두어 법 제37조⑬의 간주 효과와 충돌함(법률상 이미 수리로 간주된 신고를 행정청이 미수리로 취급). ② '법령 해석·다른 기관 협의'가 필요하면 민원처리법 시행령 제21조에 따라 연장 사유와 예정일을 문서로 통지해야 하나, 식품위생법령에는 옥외영업 변경신고에서 별표 14 제8호나목1)사)의 '관계 법령' 적합 여부를 신고인이 책임지는 준수사항으로 보는지 신고관청의 심사사항으로 보는지 규정이 없어, 심사사항으로 해석하는 지자체에서는 3일 처리기간과 구조적으로 양립할 수 없음. ③ 그 결과 별표 14의 요건 외 사유(제3자 민원, 타 부서 의견)로 수리가 지연·거부되는 경로가 열려 있고, 인터뷰이는 조문상 요건을 모두 확인하고도 결과를 예측할 수 없다고 진술.
 [논거] 행정기본법 제34조: 수리가 필요한 신고는 법률에 명시된 경우에 한하며, 식품위생법 제37조⑬은 기간 경과 시 수리 간주를 명시하므로 간주 이후의 '보류'는 법률상 근거가 없음. 행정절차법 제40조①·민원처리법 제13조: 신고 요건과 심사기준은 미리 게시해야 하므로, 법령에 특정되지 않은 '관계 법령 적합성'을 수리 요건처럼 운용하는 것은 규제 법정주의(행정규제기본법 제4조)와 예측가능성에 반함. 민원처리법 제9조①(접수 보류·거부 금지), 제27조③(거부 시 이유·구제절차 통지).
 [개정 방향] ① (시행규칙 제43조) 변경신고, 특히 영업장 면적 변경신고의 처리에 제42조⑧(신고증 발급)·⑩(발급 후 15일 이내 시설 확인)을 준용하는 항을 신설하여 '선수리·후확인' 구조를 서식이 아닌 조문에 명시. ② (시행규칙 별표 14 제8호나목1)사)) 옥외영업장 요건 중 신고관청이 확인하는 사항(예: 건축물대장상 대지 범위 내 여부, 도로 점용 여부)과 영업자 준수사항으로 두는 사항을 구분해 명시하고, 다른 법령 적합성 확인이 필요한 경우 민원처리법 시행령 제21조의 연장 통지 절차를 따르도록 규칙에 명시. ③ (법률) 제37조⑬ 간주 이후 신고증(변경사항 기재) 교부 의무를 시행규칙 제43조에 함께 신설하여 간주의 실효성 확보(연번 5와 연계). 법률 개정 없이 ①·②는 시행규칙만으로 가능.
-[유의] 식약처 소관. 2021.12.30·2026.9.1 시행규칙 개정으로 옥외영업 조문이 최근 바뀌어 개정 전후 신구대조는 원문 미대조. 인터뷰이 사례는 2026년 인천 연수구 1건으로 입법사실 규모는 제한적이나, 4개 인터뷰 모두 옥외영업 신고를 '허가처럼 운영되는' 대표 사례로 지목. 경쟁업체 민원 영향은 인터뷰이 추정. 옥외영업 허용 요건 자체를 추가하는 방향은 규제 강화로 과제 범위 밖. [교차확인] 연번 4(이종서 인터뷰), 연번 5(박정모 인터뷰)와 동일 쟁점, 검토메모 16(이범원 인터뷰) 참조.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="266" customHeight="1">
+[유의] 식약처 소관. 2021.12.30·2026.9.1 시행규칙 개정으로 옥외영업 조문이 최근 바뀌어 개정 전후 신구대조는 원문 미대조. 인터뷰이 사례는 2026년 인천 연수구 1건으로 입법사실 규모는 제한적이나, 4개 인터뷰 모두 옥외영업 신고를 '허가처럼 운영되는' 대표 사례로 지목. 경쟁업체 민원 영향은 인터뷰이 추정. 옥외영업 허용 요건 자체를 추가하는 방향은 규제 강화로 과제 범위 밖. [교차확인] 연번 5(박정모 인터뷰)와 동일 쟁점. 검토메모 22(이종서 인터뷰, 사용자 판단으로 본표 제외)·14(이범원 인터뷰) 참조.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="292" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>2026.8.25.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>행정사</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>사이 행정사무소·정은지(행정사)(기업 인허가·인증, 개인사업자·법인 인허가·면허·등록, 출입국)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>민원 처리에 관한 법률 제8조, 제8조의2제1항, 제12조의2제1항, 제22조제1항·제3항
+민원 처리에 관한 법률 시행령 제5조, 제5조의2제1항·제2항, 제6조제8항, 제24조제1항~제4항
+행정절차법 제17조제5항, 제40조제3항, 같은 법 시행령 제11조제1호
+전자정부법 제7조제1항·제3항·제5항</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>[인터뷰 내용] 보완 요구는 담당자 해석 차이로 지역마다 불필요한 서류가 갑자기 추가되는 형태로 발생하고, 이메일로 보완하겠다고 하면 '절대 안 된다'며 방문을 요구하는 담당자가 있으며 이는 재량으로 운용됨. 담당 신고 업무 중 보완 때문에 방문하라는 경우가 30~40%로 추정되고 왕복 시간·교통비가 신고인의 추가 비용으로 발생. 보완기간은 처리기간에서 제외되어 법정 처리기간 준수에는 영향이 없음.
+[발언] 정은지: "말씀드린 것처럼 이제 어떤 지역은 이게 필요가 없는 서류인데 갑자기 이제 필요한 서류들이 막 생겨요.이제 어떻게 보면 이제 담당자 해석의 차이로 인해 그런 경우가 발생하는 것 같아요." / 정은지: "네, 그렇죠. 왜 아까처럼 무조건 방문만 하라고 하는 경우에는 가야 되고 또 이제 왔다 갔다 하는 시간 낭비나 교통비 이런 것들이 좀 있을 수 있죠." / (면담자 이민아) "그러면 지금 보완 요구할 때 제일 이제 비용이 많이 드는 게 시간적으로 방문하라고 하는 게 제일 부담스러워하실 것 같은데 그러면 전체 담당하시는 신고 업무들이 100%라고 치면 그전에 보완 요구 때문에 오라고 하는 경우가 한 몇 퍼센트 정도 돼요?" 정은지: "한 3-40% 정도요" / 정은지: "네. 저희가 이제 이메일로 보완하면 안 되겠냐라고 하면 절대 안 된다고 이렇게 하는 분도 있어요." / (면담자 이민아) "그것도 아까 재량인가요?" 정은지: "네, 재량이에요." / 정은지: "네네 맞아요. 저희가 보완하는 그 기간에 어차피 빼잖아요. 처리 기간에서 빼가지고."</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>[현행 규정] 민원처리법 제8조: 민원 신청은 문서(전자문서 포함)로 함. 제8조의2①: '민원인은 민원의 처리에 필요한 증명서류나 구비서류를 「전자정부법」 제2조제7호에 따른 전자문서나 같은 조 제8호에 따른 전자화문서로 제출할 수 있다. 다만, 행정기관이 전자문서나 전자화문서로 증명서류나 구비서류를 받을 수 있는 정보시스템을 구축하지 아니한 경우 등 대통령령으로 정하는 사유가 있는 경우에는 그러하지 아니하다.' 제22조①: 보완이 필요하면 상당한 기간을 정하여 지체 없이 보완 요구, ③: 보완 절차·방법은 대통령령. 시행령 제5조: 직접 방문이 필요 없는 민원은 정보통신망·우편 등으로 신청 가능. 제5조의2①: 전자 제출의 예외 = 1. 전자문서를 받을 수 있는 정보시스템을 구축하지 않은 경우, 2. 시스템 장애, 3. 판독 불가 수신, 4. 다른 법령의 별도 규정; ②: 그 경우 지체 없이 알리고 방문·우편·팩스 등 다른 방법을 안내. 제24조①: 보완 '요구'는 문서 또는 구술 등으로(민원인이 요청하면 문서), ②~④: 보완기간 연장·재요구·기간 계산 — 민원인이 보완서류를 제출하는 방법은 규정하지 않음. 제6조⑧: 전자민원창구 신청은 도달 후 8근무시간 이내 접수. 행정절차법 시행령 제11조1호: 보완 소요 기간(보완을 위해 신청서를 신청인에게 발송한 날과 보완되어 행정청에 도달한 날 포함)은 처리기간에 불산입. 법 제12조의2①: 행정기관의 장은 민원인이 방문하지 않고도 민원을 처리할 수 있도록 관계법령 개선·정보시스템 구축 등 필요한 조치를 하여야 함.
+[문제점] ① 제8조의2①이 구비서류의 전자 제출을 민원인의 권리로 규정했으나 보완 단계에 적용된다는 명시가 없고, 시행령 제24조는 행정청의 보완 '요구' 방법만 규정하여 '신청은 전자로, 보완은 방문으로'라는 운용을 막는 조문이 없음(인터뷰: 이메일 보완 '절대 안 된다', '재량'). ② 제8조의2① 단서와 시행령 제5조의2①1호의 예외가 '행정기관이 정보시스템을 구축하지 아니한 경우'로 되어 있어, 전자민원창구에 보완서류 제출 기능을 두지 않은 기관은 자신의 미구축을 이유로 전자 제출을 거부할 수 있고 구축 기한이나 최소 기능에 관한 의무가 없어 예외가 사실상 재량처럼 작동함. ③ 보완기간은 처리기간에 산입되지 않으므로(행정절차법 시행령 제11조1호) 방문 보완 요구는 법정 처리기간 통계에 드러나지 않은 채 신고인의 시간·교통비만 늘림(인터뷰이 추정: 보완 요구 중 방문 요구 30~40%).
+[논거] 민원처리법 제12조의2①(비방문 처리를 위한 법령 개선·시스템 구축 의무)과 제8조의2①(전자 제출 권리)의 취지상 보완도 신청과 같은 방법으로 할 수 있어야 하고, 보완은 신청의 연장이므로 신청보다 엄격한 방식을 요구할 합리적 이유가 없음(비례원칙). 전자정부법 제7조①·③: 관계 법령이 종이문서를 정하고 있어도 전자문서·전자화문서로 신청·첨부 가능. 행정절차법 시행령 제11조1호가 보완서류의 '발송·도달'을 전제하는 것과 체계상 부합. 체계 정합성: 신청(제8조·시행령 제5조), 접수(시행령 제6조⑧), 결과 통지(법 제27조②)는 전자 처리가 명문화되어 있고 보완 단계만 공백.
+[개정 방향] ① (시행령 제24조) 신설 항: '민원인은 제1항에 따라 요구받은 보완을 법 제8조의2제1항에 따른 전자문서·전자화문서 또는 제5조에 따른 방법으로 할 수 있다. 이 경우 제5조의2를 준용한다.' ② (시행령 제24조①) 보완을 요구할 때 보완의 방법과 보완기간이 처리기간에 산입되지 않는다는 사실을 함께 알리도록 명시. ③ (시행령 제5조의2①1호) '정보시스템을 구축하지 않은 경우'에 '통합전자민원창구를 통하여 받을 수 있는 경우는 제외한다'를 추가하여, 정부24 등 통합창구로 받을 수 있으면 미구축 예외를 원용할 수 없도록 함. ④ 시스템: 정부24 접수 민원의 보완서류 업로드 기능 — 운영 사항. ①~③은 대통령령 개정으로 가능(법률 개정 불요).
+[유의] 행정안전부 소관(법무담당관 직접 심사 대상). 법령 대조 과정에서 제8조의2①(구비서류 전자 제출 권리)이 확인되어 이 쟁점은 '근거 부재'가 아니라 '보완 단계 적용 명시 부재와 예외 조항의 폭' 문제로 성격이 바뀜 — 운영 위반 성격이 강하므로 본표 수록은 사용자 판단(2026.10.15, 1차 검토메모에서 격상)에 따른 것임. 단일 인터뷰(정은지) 입법사실이며 30~40%는 인터뷰이 추정치. 이메일이 제8조의2의 '정보시스템'을 통한 제출에 해당하는지는 행안부 해석 확인이 필요하여, 개정 방향은 전자민원창구·정보통신망 제출 보장으로 한정하고 이메일 접수 의무화는 제안하지 않음. 박정모(8.26)도 보완 인정 기준이 해마다 바뀐다고 언급했으나 전자 제출 거부를 직접 진술하지는 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="266" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>2026.8.26.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>행정사</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>청연 행정사 사무소·이종서(행정사)(기업 인증(벤처·이노비즈·기업부설연구소), 폐기물 인허가, 평생교육시설, 동물 관련 영업, 노인복지시설)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>식품위생법 제37조제4항·제12항·제13항
 식품위생법 시행규칙 제42조제3항(개정 2020.4.13), 별표 14 제8호가목5)가)(7)·(9) 및 제2호사목3)·6), 별지 제37호서식(한시적 영업신고 수수료란)
@@ -573,42 +616,42 @@
 행정규제기본법 제4조제1항</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>[인터뷰 내용] 영업신고를 마친 음식점이 축제·페스티벌에 참가할 때 하는 한시적 영업신고에서, 어떤 지자체는 지자체 주최 행사만 허용하고 민간 주최 맥주축제 등은 불허하는 반면 다른 지자체는 주최자를 묻지 않고 장소의 위생만 본다. 조례에도 상위법에도 근거가 없는 재량으로 보이고, 불허 사유 설명도 없으며, 정부24에는 온라인 신고가 가능하다고만 표시되어 지자체별 제한을 알 수 없다. 전국을 도는 업주가 다른 지역에서 신고 없이 참여하게 되는 결과가 생김.
 [발언] 이종서: "이게 쉽게 말해서 치킨집 하시는 분들이 정상적으로 영업 허가를 받으신 분들이죠. 이분들이 어떤 축제라든가 어떤 페스티벌에 나갈 때 한시적으로 거기서 팔 수 있게 되거든요. 그때도 영업 신고를 하긴 해야 되거든요." / 이종서: "근데 어떤 지역은 지자체에서 주최한 음식 페스티벌만 한시적 영업 신고가 가능하다라고 하는 곳이 있고. 그러니까 하지 말라는 거예요. 지자체가 아니고 민간 업체가 주도한 맥주 축제 이런 거는 당신들은 여기 참여할 수 없어 이렇게 돼 있어요. 근데 어떤 지역은 민간이든 지자체가 주최하든 그건 아무 상관이 없어요. 그건 상관이 없고 그 장소만 본다는 거죠. 장소가 위생적으로 괜찮고 공간을 활용한가." / 이종서: "그러니까 사실 근데 이게 확인해 보면 조례에 의한 것도 아니에요. 조례에 의해서 우리 군은 한시적 영업 신고 여기에서 안 됩니다라고 규정돼 있지 않더라고요." / 이종서: "그냥 재량이었던 거죠. 아예 상위법에도 규정이 없어요. 그래서 이 한시적 영업 신고 이거에 대해서는 모르겠어요. 이런 것들이 그냥 재량껏 되는 거고. 그거에 대한 명확한 근거 자료나 제가 이런 것도 받아본 적이 없어요." / (면담자 오세영) "반려 사유에 대한 설명이 없다?" 이종서: "예. 그냥 그 지역 안 된다." / 이종서: "네, 100% 온라인 신고 가능한 것 중에 아까 한시적 영업 신고거든요. 그게 100% 온라인으로 딱 가능하거든요. 전화도 안 해도 되고 근데 아이러니하게 그런 리스크가 있으니까 확인을 해야 되는 거죠. 안 되는 경우가 많기 때문에 그러니까 그 시스템에는 그런 거가 안 써 있어요. 당연히 지자체별로 조례나 뭐 이런 거에 대해서 안 될 수가 있다라는 문구가 없어요." / 이종서: "업주분들 중에 전국을 도는 분들이 있어요. 같은 거 가지고. 그러니까 당연히 여기에서 청주에서 됐으니까 지역마다 확인 안 하시고 그럼 여기도 당연히 되겠지 하고 모든 걸 준비를 했는데 안 된다는 거예요. 그러면은 영업 신고 없이 무허가로 참여하게 되는 꼴이 돼버리는 거죠."</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>[현행 규정] 식품위생법 시행규칙 제42조③(개정 2020.4.13): '신고한 영업소 외의 다른 장소(제2호의 경우에는 별표 14 제8호가목5)에 따른 장소만 해당한다)에서 1개월의 범위에서 한시적으로 영업을 하려는 자'는 영업신고증(즉석판매제조·가공업은 자가품질검사 결과서 포함)을 관할 신고관청에 제출. 별표 14 제8호가목5)가)는 시설기준 적용특례 장소를 (1)~(9)로 열거하며 행사 관련 항목은 '(7) 지방자치단체의 장이 주최, 주관 또는 후원하는 지역행사 등'과 '(9) 그 밖에 특별자치시장ㆍ특별자치도지사ㆍ시장ㆍ군수ㆍ구청장이 별도로 지정하는 장소'. 즉석판매제조·가공업도 제2호사목3)·6)에서 같은 구조. 지정의 기준·절차·공표에 관한 규정은 없음. 별지 제37호서식 수수료란에 '제42조제3항에 따른 한시적 영업신고' 8,300원(전자)·9,300원(방문)이 있어 영업신고서 서식으로 접수되는 구조.
 [문제점] ① 민간이 주최하는 축제·행사는 열거 항목에 없고 (9)의 '별도 지정'에만 의존하므로, 지정 여부가 전적으로 지자체 재량이 되어 같은 행사 유형에 대해 A군은 허용·B군은 불허하는 편차가 법령 구조 자체에서 발생함(인터뷰: 지자체 주최 행사만 허용 vs 장소 위생만 심사). ② (9)의 지정에 기준·절차·공표 의무가 없어 신고인이 사전에 가능 여부를 알 수 없고, 불허 시에도 '그 지역은 안 된다' 외에 이유가 제시되지 않음(행정절차법 제23조①). ③ 정부24에 온라인 신고 가능으로 표시되나 별표 14의 장소 요건과 지자체별 지정 현황은 안내되지 않아 행정절차법 제40조①(신고 요건 게시 의무)과 괴리. ④ 수범자인 행정사조차 '상위법에 규정이 없다'고 인식할 정도로 특례 규정이 별표 깊숙이 있어 접근성이 낮고, 제42조③이 '영업신고증 제출'로만 규정되어 법 제37조⑫의 3일 내 수리 통지가 적용되는 신고인지 문언상 불명확.
 [논거] 행정규제기본법 제4조①: 규제 내용은 '알기 쉬운 용어로 구체적이고 명확하게' 규정. 행정절차법 제40조①: 신고 요건·접수기관 등 게시 의무. 평등원칙·예측가능성: 조례 위임도 없이 지자체 지정 유무에 따라 동일 법령의 허용 범위가 달라지는 것은 법령이 스스로 편차를 허용한 구조. 동일 지역에서 지자체 행사와 민간 행사의 위생 위험이 주최자에 따라 달라지지 않으므로 '주최·주관·후원' 요건은 수단의 적합성이 약함.
 [개정 방향] ① (시행규칙 별표 14 제8호가목5)가) 및 제2호사목) (7)에 '민간이 주최하는 지역행사로서 특별자치시장ㆍ특별자치도지사ㆍ시장ㆍ군수ㆍ구청장이 위생ㆍ안전 관리계획을 확인한 행사'를 추가하거나, (9)에 '지정 기준과 지정 장소를 미리 정하여 공표하여야 한다'는 단서를 신설. ② (시행규칙 제42조③) 한시적 영업신고에 법 제37조⑫·⑬이 적용됨을 명시하고 불허 시 사유 통지를 민원처리법 제27조③에 따라 운용하도록 규정. ③ (시스템·운영) 정부24 한시적 영업신고 안내에 별표 14 장소 요건과 지자체별 지정 장소 링크 표시 — 운영 사항.
-[유의] 식약처 소관. 인터뷰이 발언('상위법에도 규정이 없다', '조례에 의한 것도 아니다')은 법령 확인 결과와 다름 — 규정은 있으나 민간 행사 허용 여부가 지자체 지정에 위임된 구조이며, 그 차이는 검토메모 25에 기록. 민간 행사 포함은 특례 범위 확대(규제 완화)로 신고제도 범위 내이나 위생사고 위험에 대한 식약처 입장 확인 필요. 지자체 안내문(진안군 등) 등 2차 자료는 접속 차단으로 원문 미확인. 특정 지자체(허용·불허 사례의 지역명)가 발언에서 특정되지 않아 지자체 간 편차 주장은 입법사실로서 보강이 필요함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="227" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+[유의] 식약처 소관. 인터뷰이 발언('상위법에도 규정이 없다', '조례에 의한 것도 아니다')은 법령 확인 결과와 다름 — 규정은 있으나 민간 행사 허용 여부가 지자체 지정에 위임된 구조이며, 그 차이는 검토메모 24에 기록. 민간 행사 포함은 특례 범위 확대(규제 완화)로 신고제도 범위 내이나 위생사고 위험에 대한 식약처 입장 확인 필요. 지자체 안내문(진안군 등) 등 2차 자료는 접속 차단으로 원문 미확인. 특정 지자체(허용·불허 사례의 지역명)가 발언에서 특정되지 않아 지자체 간 편차 주장은 입법사실로서 보강이 필요함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="227" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2026.8.26.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>행정사</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>청연 행정사 사무소·이종서(행정사)(기업 인증(벤처·이노비즈·기업부설연구소), 폐기물 인허가, 평생교육시설, 동물 관련 영업, 노인복지시설)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>평생교육법 제33조제2항, 제35조제2항, 제36조제3항, 제37조제3항, 제38조제3항, 제38조의2
 평생교육법 시행령 제48조, 제49조제1항·제3항, 제64조제2항, 제65조제2항(원문 미대조), 제66조제2항, 제67조제2항
@@ -616,13 +659,13 @@
 행정기본법 제34조, 행정절차법 제40조제2항~제4항</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>[인터뷰 내용] 민간 자격증·취미 교육(공방 등)을 위한 평생교육시설 설치는 법률상 '설치 신고'이지만 운영규칙·커리큘럼·소방·건축 요건 등 서류가 상당하고 반려가 많아 '등록 이상'으로 운영됨. 원격 시설은 완화되어 있으나 오프라인 시설은 요건이 많음. 바우처(평생교육이용권) 수요로 신고 수요가 늘고 있음.
 [발언] 이종서: "그렇죠 많이 하시죠. 왜냐면은 자격증 같은 것도 이제 민간으로 하려고 하시는 분들, 이것도 이제 신고 말은 설치 신고거든요. 설치 신고인데 그게 이제 서류나 뭐 이런 것들이 상당해요. 그 내용부터 해가지고 그리고 이것도 이제 반려하는 경우가 되게 많습니다. 이제 꾸려야 되는 커리큘럼이라든가 운영이라든가 그리고 또 오프라인 교육장 시설 소방시설부터 해가지고 건축법 또 맞춰야 되죠. 그런 것들을 해가지고 근데 말은 신고인데 거의 등록 이상인 것 같아요." / 이종서: "그렇죠. 이제 원격 평생교육 시설은 조금 완화가 돼 있고 지금 오프라인 경우에는 설치 요건이 조금 더 많죠." / 이종서: "그냥 민간인들도 많이 하세요. 최근에 했던 게 소잉이라고 해가지고 말 그대로 공방인 거죠. 평생교육 시설이 일반인이 할 수 있는 분야가 있고 언론기관, 회사의 부서 안, 대학 부설 기존엔 그렇게 많이 했었죠." / 이종서: "그렇죠. 폐기물 인허가 이런 것들 그리고 이제 평생교육 시설 같은 경우에도 그런 것들로 사업 계획서를 꾸려야 돼요."</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>[현행 규정] 평생교육법 제33조②: 원격교육 형태 평생교육시설은 '대통령령으로 정하는 바에 따라 교육감에게 신고하여야 한다'. 제35조②(사업장 부설)·제36조③(시민사회단체 부설)·제37조③(언론기관 부설)·제38조③(지식·인력개발 관련)도 같은 문언. 법률에는 수리 여부 통지 기한, 수리 간주, 수리 거부 사유 규정이 없음. 시행령 제49조③: '교육감은 제1항에 따른 신고가 있는 경우에는 이를 검토하여 요건에 해당하면 교육부령으로 정하는 신고증을 내주어야 한다'(제64조②·제66조②·제67조②에서 준용). 시행규칙 제17조②: 첨부서류 8종(위치도·시설배치도·시설설비 현황표·평생교육사 자격증·정관·회의록·재산목록 및 증명서류·임대차계약서 사본). 별지 제14호서식(개정 2024.6.18): 처리기간 10일, 처리절차 '접수 및 검토→결재→신고증 작성→대장 기재→교부'.
 [문제점] ① 법률은 '신고'만 규정하고 수리를 명시하지 않았는데 시행령이 '검토하여 요건에 해당하면 신고증 교부'라는 심사형 절차를 두어, 수리가 필요한 신고는 법률에 명시하도록 한 행정기본법 제34조와의 정합성 문제가 있음. 수리 필요 신고라면 법률에 근거가, 자기완결적 신고라면 행정절차법 제40조②에 따라 형식 요건 구비 시 도달로 의무가 이행되어야 하는데 어느 쪽인지 법문상 불명확하여 교육청이 실질 심사·반려를 반복(인터뷰: '반려하는 경우가 되게 많습니다', '거의 등록 이상'). ② 처리기간 10일은 서식에만 있고 법령에 수리 여부 통지 기한·간주 규정이 없어, 2018~2019년 신고제도 정비에서 채택된 표준(식품위생법 제37조⑫⑬, 폐기물관리법 제46조③④ 등)에서 누락된 형태. ③ '요건'의 내용이 시행령 제49조①·②의 신고서·운영규칙 기재사항 수준에 머물러 어떤 사유로 반려되는지 예측하기 어렵고, 소방·건축 요건은 시설기준 조문이 아니라 심사 과정에서 요구됨.
@@ -632,49 +675,6 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="188" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026.8.26.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>행정사</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>청연 행정사 사무소·이종서(행정사)(기업 인증(벤처·이노비즈·기업부설연구소), 폐기물 인허가, 평생교육시설, 동물 관련 영업, 노인복지시설)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>식품위생법 제37조제4항·제12항·제13항
-식품위생법 시행규칙 제42조제8항·제10항, 제43조제1항제2호·제2항, 별표 14 제8호나목1)사), 별지 제41호서식
-민원 처리에 관한 법률 시행령 제21조제1항제1호·제2호
-행정절차법 제40조제1항</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 보완 요구가 나오는 대표 사례가 옥외영업(테라스) 신고. 도로법 등 여러 유관 부서가 관련되어 신고인이 모든 요건을 사전에 확인하기 어렵고 행정청도 미리 알려주지 않으며, '나와서 봐야 알 수 있다'며 현장 확인 뒤 통행로 폭 등으로 보완을 요구함. 서류상 보완은 많지 않음. 지자체에 따라 처리 결과를 통보하지 않아 신고인이 전화로 확인해야 하는 경우도 있음.
-[발언] 이종서: "어쩔 수 없이 뭐 나온다고 하면은 유관 부서와 관련된 건들 그리고 예를 들면은 옥외영업 신고라는 게 있거든요. 그러니까 테라스 밖에서 이제 음식 이렇게 하고 이런 것들 있지 않습니까? 이런 것들도 도로법부터 해가지고 여러 가지 유관 부서가 있다 보니까 모든 거는 체크하기 어려운 경우가 있거든요. 그리고 미리 얘기해 주지 않는 경우가 있죠." / 이종서: "일단 우리가 나와서 봐야 알 수 있다라고 하기 때문에 도면으로 보는 것과 실제로 나갔을 때 그게 다른 경우가 있을 수 있거든요. 그런 것들이 보완이 올 수가 있죠. 예를 들면은 여기 통행로가 도면상으로는 5m인데 실제로 나가 보니까 한 4점 몇 미터가 측정이 됐다든가. 그렇게 되면은 의자를 조금 더 치워가지고 통로를 확보를 하고 이런 것들인 거죠. 굳이 따지자면 그런 것들이 있고 서류적인 보완은 그렇게 크게 있진 않아요." / 이종서: "이것도 지자체에 따라 다르긴 한데 이게 결과가 나왔는지 안 나왔는지 통보를 안 해줍니다. 그러니까 그 날짜 되면 알아서 찾아가라는 경우가 있어요. 이걸 전화를 해서 확인을 해야 돼요."</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[현행 규정] 연번 1과 같은 조문. 특히 시행규칙 제42조⑧은 영업신고를 받으면 '지체 없이' 신고증을 발급하고, ⑩은 신고증 발급 후 15일(식품접객업은 1개월) 이내에 시설을 확인하도록 하여 신규 신고에 대해서는 '선 신고증·후 확인' 구조를 조문으로 두었음. 그러나 변경신고를 규정한 제43조에는 신고증 발급·사후 시설확인 조항이 없고, 별지 제41호서식의 처리절차에만 '신고증 발급→필요시 시설조사(15일 이내)'가 표기됨. 별표 14 제8호나목1)사)의 '건축법 등 관계 법령' 적합 요건은 통행로 폭 등 현장 사실에 따라 달라짐.
-[문제점] ① 옥외영업 변경신고에 대해 조문(제43조)에는 사후 확인 근거가 없으므로 신고관청이 서식과 달리 '사전 현장 확인 후 수리'로 운용할 여지가 생기고, 그 결과 신고인은 접수 후 현장 확인 일정까지 영업 개시 시점을 예측할 수 없음. ② 통행로 폭·안전시설 같은 현장 요건은 별표 14에 수치 기준이 없어 보완 요구의 내용이 지자체·담당자별로 달라지고, 유관 부서(도로·건축)의 의견을 어느 단계에서 어떻게 반영하는지 절차가 없음. ③ 수리 결과를 통보하지 않고 '날짜가 되면 찾아가라'는 운용은 민원처리법 제27조①에 어긋나는 운영 문제이나, 변경신고에 신고증 재발급 조항이 없어 통지의 매개(신고증)가 법령상 특정되지 않은 점이 이를 뒷받침.
-[논거] 행정절차법 제40조①: 신고에 필요한 사항은 미리 게시해야 하므로 현장 확인에서 비로소 드러나는 요건은 사전 게시 의무와 충돌함. 상·하위법령 정합성: 서식(별지 제41호)의 처리절차가 조문(제43조)에 근거를 두지 않음. 민원처리법 시행령 제21조①2호: 현장 확인이 필요한 경우 처리기간 연장과 문서 통지로 처리해야 하며 수리를 미루는 방식은 허용되지 않음.
-[개정 방향] ① (시행규칙 제43조) 신설 항: '제1항에 따른 변경신고를 받은 신고관청은 제42조제8항·제10항을 준용하여 영업신고증에 변경사항을 적어 재발급하고, 필요한 경우 발급 후 15일 이내에 변경사항을 확인한다.' ② (별표 14 제8호나목1)사)) 옥외영업장의 통행로 확보 폭 등 신고관청이 확인할 최소 기준을 명시하거나, 적용 법령(도로법·건축법 등)의 조문을 특정하여 신고인이 사전에 확인할 수 있게 함. ③ 운영: 현장 확인이 필요한 경우 민원처리법 시행령 제21조③에 따른 연장 통지 이행 — 식약처 지침 사항.
-[유의] 식약처 소관. 인터뷰이는 서류상 보완은 많지 않고 현장 요건 보완이 주된 유형이라고 하여, 쟁점을 '현장 요건의 사전 명확화'로 한정함. 통행로 폭 기준을 별표에 추가하는 것은 기준 명시(기존 운용 기준의 명문화)이지 요건 신설이 아니라는 전제이나, 수치 기준이 지역 여건별로 달라야 한다는 반론 가능(규제영향 검토 필요). [교차확인] 연번 1(정은지 인터뷰), 연번 5(박정모 인터뷰)와 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="227" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
@@ -714,17 +714,17 @@
 [문제점] ① 종로구 사례는 법 제37조⑬에 따라 3일 경과 다음 날 이미 수리 간주된 상태였는데도 신고인은 이를 알 수 없었고 신고증도 받지 못했음 — 간주의 법적 효과가 신고인에게 전달되는 수단(통지·신고증)이 변경신고에 관하여는 법령에 특정되어 있지 않음. ② 제43조에는 변경신고 수리(간주 포함) 후 신고증 기재·재발급 조항이 없고 서식에만 '신고증 발급'이 표기되어 조문과 서식이 불일치하며, 신고증 첨부 의무도 조문 없이 서식 유의사항에만 전제됨. ③ 영업신고증은 영업장 비치·점검 대상이라는 실무 전제(인터뷰이: '어차피 가서 받는 서류')에서, 간주 후에도 신고인이 방문해 재발급을 요청해야 하면 수리 간주는 지연 통제 수단으로 기능하지 못함.
 [논거] 상·하위법령 정합성(법률의 수리 간주 ↔ 시행규칙의 신고증 절차 공백 ↔ 서식의 처리절차 표기). 민원처리법 제27조①·시행령 제29조①: 처리 완료 시 지체 없이 교부 또는 정보통신망·우편 통지 의무 — 간주로 처리가 완료된 경우에도 적용된다고 보아야 하나 명문 규정 없음. 전자정부법 제7조②·민원처리법 제27조②: 전자문서 신고증 교부가 가능하므로 '자동 출력'은 법령상 장애가 없고 시행규칙에 근거만 두면 됨.
 [개정 방향] ① (시행규칙 제43조) 신설 항: '신고관청은 변경신고를 수리(법 제37조제13항에 따라 수리한 것으로 보는 경우를 포함한다)한 때에는 지체 없이 영업신고증에 변경사항을 적어 재발급(전자문서를 포함한다)하여야 한다.' 및 변경신고 시 신고증 첨부 또는 분실 시 사유 기재 규정을 조문으로 이관. ② (법률 또는 법제처 표준문안) 수리 간주 조항에 '간주된 경우 행정청은 신고인의 요청 없이 신고증을 교부하여야 한다'는 후속 절차를 범정부 표준으로 추가하는 방안 검토(식품위생법 제37조⑬에 우선 반영). ③ 운영: 담당자 미결재는 민원처리법 시행령 제21조②(담당자 부재 등을 사유로 한 연장 금지, 2026.5.6 신설)와 제22조 처리상황 확인·점검 사항.
-[유의] 식약처 소관(①), 법제처·행안부 협의(②). 담당자가 결재를 올리지 않은 것 자체는 운영 문제이며 본표에 올린 것은 간주 후속 절차의 법령 공백에 한정함. 인터뷰이 사례는 2026년 종로구 1건이고 인터뷰이 본인 의견('수리 폐지는 안 된다', '간주는 실효성 없다')은 정책 선호로서 기록만 함. [교차확인] 연번 1(정은지 인터뷰), 연번 4(이종서 인터뷰)와 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="214" customHeight="1">
+[유의] 식약처 소관(①), 법제처·행안부 협의(②). 담당자가 결재를 올리지 않은 것 자체는 운영 문제이며 본표에 올린 것은 간주 후속 절차의 법령 공백에 한정함. 인터뷰이 사례는 2026년 종로구 1건이고 인터뷰이 본인 의견('수리 폐지는 안 된다', '간주는 실효성 없다')은 정책 선호로서 기록만 함. [교차확인] 연번 1(정은지 인터뷰)와 동일 쟁점. 검토메모 22(이종서 인터뷰, 사용자 판단으로 본표 제외) 참조.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="253" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026.8.26.</t>
+          <t>2026.8.28.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -734,54 +734,10 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>행정사 사무소 법연·박정모(행정사)(외국인 출입국 업무, 소상공인·중소기업 신고·인허가)</t>
+          <t>으뜸퍼스트 행정사사무소·이범원(행정사)(출입국, 건설업 등록, 식품·축산물 HACCP 인허가, 공장등록)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>행정사법 제10조제1항, 제11조제1항·제2항(개정 2020.6.9), 제12조제1항
-행정사법 시행령 제20조제1항~제3항(제3항 신설 2025.10.10)
-행정사법 시행규칙 제7조제1항, 제9조, 별지 제8호서식(개정 2025.11.20, 처리기간 10일)
-민원 처리에 관한 법률 제17조제1항·제19조제2항
-행정기본법 제34조</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 행정사 개업 시 업무신고(인터뷰이는 '영업신고'로 표현) 처리기간은 10일로 잡혀 있으나 지역마다 3일에 내주는 곳과 보름 걸리는 곳이 있고, 신고확인증이 나와야 출입국 대행기관 교육·등록 차수를 맞출 수 있어 지연 시 한 달까지 밀림. 종로구는 3일, 은평구는 일주일이 넘어도 연락이 없어 전화하자 '지금 오시면 바로 준다'고 함. 기한을 넘기면 이유를 설명받고 싶다고 함.
-[발언] 박정모: "가령 행정사의 경우 개업할 때 영업 신고하고 세무소 가서 사업자 등록하고 사업자 등록증을 출입국에 제출해서 대행 기관 등록을 받아야 돼요. 행정사의 영업신고는 10일이 잡혀 있거든요? 근데 각 지역마다 3일 만에 해 주는 데가 있고 보름 만에 해 주는 데가 있어요. 저희도 이제 교육 일정이나 이런 게 있기 때문에 그게 나와야 출입국 가서 교육도 받고 출입국 대행기관 등록도 하는데, 그것도 이제 차수가 있잖아요? 이 차수를 놓치면은 1주, 2주, 그리고 한 달까지 넘어가니까 저희 입장에서는 이제 굉장히 좀 답답하죠." / 박정모: "한국인한테 비슷한 예로, 제가 올해 초에 동기들과 영업 신고를 했는데 종로구는 3일 만에 나오더라고요. 근데 여기 은평구는 일주일이 넘었는데도 연락이 없어요. 그래서 전화를 해봤어요. 그랬더니 지금 오시면 바로 준대요. 그렇다고 해가지고 매일 공무원한테 하루에 한 번씩 전화할 수는 없는 문제잖아요. 그러다 보니까 이건 이제 편차도 굉장히 좀 큰 것 같고요." / 박정모: "보통은 안 해요. 그래서 이게 왜 넘어갔는지를 좀 설명을 듣고 싶은데."</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>[현행 규정] 행정사법 제10조①: 행정사 자격자가 업무를 하려면 대통령령으로 정하는 업무신고 기준을 갖추어 시장등에게 신고. 제11조①: 기준 미달 시 수리 거부 가능, 지체 없이 거부 사실·사유 통지. 제11조②(개정 2020.6.9): '시장등이 업무신고를 받은 날부터 3개월이 지날 때까지 제12조에 따른 행정사업무신고확인증을 발급하지 아니하거나 행정사업무신고의 수리 거부 통지를 하지 아니하면 3개월이 되는 날의 다음 날에 행정사업무신고가 수리된 것으로 본다.' 제12조①: 신고를 받은 때 내용 확인 후 신고확인증 발급. 시행령 제20조①: 신고 기준 4개(결격사유 없음, 실무교육 이수, 자격증, 행정사회 가입), ③(신설 2025.10.10): 자격증·실무교육 수료증은 행정사정보시스템으로 확인. 시행규칙 별지 제8호서식(개정 2025.11.20): 처리기간 10일, 처리절차 '접수→검토→결재→신고확인증 발급'. 민원처리법 제17조①: 법정민원 처리기간을 종류별로 정하여 공표.
-[문제점] ① 서식상 처리기간(10일)과 법률상 수리 간주 기간(3개월)이 불일치하여, 10일을 넘겨도 3개월이 되기 전까지는 법적으로 '미수리' 상태가 유지되고 지연에 대한 법적 통제장치가 없음(인터뷰: 3일~보름 편차, 일주일 넘어도 무연락). ② 2018~2019년 신고제도 정비에서 채택된 표준(처리기간 내 미통지 시 그 기간이 끝난 날의 다음 날 수리 간주 — 식품위생법 제37조⑬, 폐기물관리법 제46조④ 등)과 달리 고정 '3개월'을 두어 동일 유형 신고 간 체계 정합성이 결여됨. ③ 신고 기준 4개는 모두 행정사정보시스템(시행령 제20조③)과 회원증으로 즉시 확인되는 형식 요건이어서 10일조차 긴 편이고 3개월의 간주 유보는 과잉임.
-[논거] 행정기본법 제34조: 수리가 필요한 신고임은 제11조로 법률에 명시되어 있으므로, 쟁점은 수리 지연을 통제하는 간주 시점의 적정성. 비례원칙: 형식 요건 확인에 3개월의 간주 유보는 수단의 과잉. 민원처리법 제17조①·제19조②: 처리기간은 공표된 기간(10일)으로 계산되는데 간주 시점이 그와 분리되어 있어 처리기간 규정의 실효성이 약화됨. 체계 정합성: 법제처 '신고 수리 간주' 표준 문안.
-[개정 방향] ① (법률 제11조②) '3개월'을 '10일(민원 처리 관련 법령에 따라 처리기간이 연장 또는 재연장된 경우에는 해당 처리기간)'로 바꾸고 간주 시점을 '그 기간이 끝난 날의 다음 날'로 정비. ② (법률 제12조①) 신고확인증을 전자문서로 발급할 수 있음을 명시하고 행정사정보시스템과 연계. ③ (최소 정비안) 법률 개정 전까지는 시행규칙 서식 처리기간(10일)을 유지하되 행정안전부가 10일 내 통지 이행을 점검 — 운영 사항.
-[유의] 행정안전부 소관(법무담당관의 직접 심사 대상). 인터뷰이는 행정사로서 자기 직역의 신고를 언급한 것이므로 이해관계자 진술이라는 점에 유의. 2020.6.9 개정으로 3개월 간주를 둔 경위(개정 이유)는 원문 미대조. 인터뷰이 표현 '영업신고'는 법률 용어 '업무신고'와 다름(검토메모 25 기록). 사례는 2026년 종로구·은평구 2건으로 입법사실 규모는 작음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="240" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2026.8.28.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>행정사</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>으뜸퍼스트 행정사사무소·이범원(행정사)(출입국, 건설업 등록, 식품·축산물 HACCP 인허가, 공장등록)</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>축산물 위생관리법 제9조제3항·제4항(신설 2020.4.7), 제22조제1항, 제25조
 축산물 위생관리법 시행규칙 제7조제3항(개정 2024.1.12), 제7조의3제1항·제2항·제6항, 제37조제1항, 별지 제28호서식(개정 2024.1.12)
@@ -791,19 +747,19 @@
 (비교) 식품위생법 제48조제2항·제3항, 같은 법 시행규칙 제62조</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>[인터뷰 내용] 축산물가공업(서대문구 사례)은 영업허가를 받은 뒤 품목제조보고를 하고 한국식품안전관리인증원에 HACCP 인증을 신청하는 순서인데, 구청 위생과가 품목제조보고를 받기 위해 HACCP 인증을 먼저 받아오라고 요구함. 인증에 수천만 원이 드는 데다 인증 심사는 운용 실적을 보므로 '인증 후 품목보고' 요구는 모순이며, 결국 사전 인증심사 관련 서류를 먼저 내는 방식으로 해결. 순환보직으로 담당자가 제도를 숙지하지 못하는 것이 원인으로 보임. 축산물은 2024년부터 HACCP 전면 의무.
 [발언] 이범원: "등록 이제 잘 아시겠지만 신고 등록 허가가 있는데 축산물 가공업은 좀 이제 아무래도 위생 관련돼서 허가 쪽으로 돼 있어요." / 이범원: "일반 식품은 등록제인데 거기에 이제 주 서대문에서 했었는데 이제 축산물 가공업을 하려고 그러면 해썹 인증이 기본이에요." / 이범원: "그런데 시작은 허가를 먼저 맡아야죠. 그래서 등록 관청에다가 허가를 등록을 하고 그다음에 이제 그걸 득한 다음에 한국식품인증관리원에 인증을 신청을 합니다." / 이범원: "허가를 받고 그다음에 품목 제조 보고라는 게 있어요." / 이범원: "이제 예를 들어서 햄을 만든다고 그러면 햄을 할 때 그러면 이 햄을 햄류를 또 품목 지수 보고를 신고를 해가지고 내주는 데가 구청이에요." / 이범원: "위생과 그럼 거기서 또 뭐라고 그러냐면 그거 품목 제조 받기 위해서 해썹 인증을 먼저 받아오라 이런 얘기예요." / 이범원: "그런 얘기를 해요. 엉뚱한 얘기죠. 그러면 해썹 인증을 하기 위해서는 돈이 수천만 원이 들어가는데 그거를 먼저 해놓고 품목 제조 보고를 한다." / 이범원: "그래서 그런 부분에 이제 트러블이 좀 있었었고 그래서 이제 결국은 사전 인증 심사 증을 하나 먼저 내고 이런 식으로 하는 그런 거 했는데 그거는 좀 모순이 되는 부분이에요." / 이범원: "육가공이 2024년도부터 전체가 다 그랬죠. 유제품까지 다"</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>[현행 규정] 축산물 위생관리법 제9조③(신설 2020.4.7): 축산물가공업 영업자 중 총리령으로 정하는 영업자(시행규칙 제7조③: 식육가공업·유가공업·알가공업 영업자 — 2024.1.12 개정으로 매출·종업원 단계 구분 삭제)와 식용란선별포장업·식육포장처리업 영업자는 안전관리인증기준을 '지켜야 한다'. ④: 식약처장은 지켜야 하는 영업자의 준수 여부를 심사하여 인증'할 수 있다'. 시행규칙 제7조의3①·②: 인증 신청은 인증원장에게 운용 계획서 첨부, 요건은 위생관리프로그램 운용·교육 수료; ⑥: 서류검토·현장조사로 기준 준수가 인정되면 인증서 발급. 법 제25조·시행규칙 제37조①·별지 제28호서식: 품목제조보고는 '제품생산 개시 전이나 제품생산 개시 후 7일 이내'에 제조방법설명서·소비기한 설정사유서 등 3종을 첨부하여 허가관청에 제출 — HACCP 인증서는 첨부서류가 아님. 고시 제4조②: 의무적용 시기는 '각 법에서 정한 바에 따르되' 매출·종업원 기준, ③: 신규영업은 3개월 매출로 산정 가능·시설 개보수 시 1년 유예, ⑤: 시행규칙 제7조③1호가목(2024.1.12 삭제) 참조. 전면 의무화 이후 신규 축산물가공업자가 언제까지 인증을 받아야 하는지, 인증 전 생산·판매가 가능한지 정하는 조문은 법·령·규칙·고시 어디에도 없음.
 [문제점] ① 품목제조보고 첨부서류에 없는 HACCP 인증서를 허가관청(구청 위생과)이 선행 요구한 것은 민원처리법 제10조①(관계법령 외 서류 요구 금지) 위반이고, 인증 심사가 실제 운용 상태(현장조사)를 전제하므로 '인증 후 품목보고'는 절차 순서가 뒤바뀐 요구임. ② 근본 원인은 법 제9조③의 '지켜야 한다'와 ④의 '인증할 수 있다' 사이에, 의무적용 영업자가 ⓐ 인증 전에 영업·생산을 개시할 수 있는지, ⓑ 언제까지 인증을 신청·취득해야 하는지가 규정되지 않은 공백이며, 지자체가 이를 '인증 완료 후 생산'으로 보수적으로 해석하면 품목제조보고 단계에서 인증을 요구하게 됨. ③ 2024.1.12 전면 의무화 이후에도 고시 제4조⑤가 삭제된 시행규칙 조문을 참조하는 등 구법 체계의 문언이 남아 신규 영업자에게 적용되는 유예·기한을 읽어낼 수 없음.
 [논거] 규제 법정주의(행정규제기본법 제4조): 인증 취득 시한과 인증 전 영업 가능 여부는 영업자의 의무 범위를 정하는 사항이므로 법령에 명확히 규정되어야 함. 민원처리법 제10조①. 체계 정합성: 식품위생법 제48조②·③도 같은 '준수 의무 + 인증 가능' 구조이고 시행규칙 제62조①13호(매출 100억 기준)가 적용 시기를 정하므로, 축산물에도 적용 시기·기한 조문이 대응되어야 함. 신뢰보호: 영업허가(제22조)와 품목제조보고를 적법하게 마친 영업자가 인증 전 생산을 위법으로 취급받을 위험.
 [개정 방향] ① (법률 제9조 또는 시행규칙 제7조) 의무적용 영업자는 '영업허가를 받은 날(또는 해당 품목의 제조 개시일)부터 ○개월 이내에 제4항에 따른 인증을 신청하여야 하며, 인증 심사가 진행되는 기간 중에는 안전관리인증기준을 준수하여 생산·판매할 수 있다'는 취지의 신청 기한·과도기 규정 신설. ② (시행규칙 제37조①·별지 제28호서식) 첨부서류가 한정적 열거임과 인증서 제출 요구 불가를 서식 안내에 명시 — 운영 보조. ③ (고시 제4조⑤) 삭제된 시행규칙 조문을 참조하는 문언 정비.
-[유의] 식약처 소관. 인증 신청 기한 신설은 이미 적용 중인 의무의 이행 시기를 명확화하는 것이지만 기한 설정 자체가 영업자 부담으로 해석될 수 있어 규제영향 검토가 필요 → 사용자 판단 필요 항목. 법률 용어는 '품목제조보고'(보고)이고 인터뷰이는 '신고'로 표현함(검토메모 25). 사례는 서대문구 1건. 식품위생법 제48조 체계와의 세부 비교는 시행규칙 제62조만 확인하고 고시의 식품 부분은 미대조.</t>
+[유의] 식약처 소관. 인증 신청 기한 신설은 이미 적용 중인 의무의 이행 시기를 명확화하는 것이지만 기한 설정 자체가 영업자 부담으로 해석될 수 있어 규제영향 검토가 필요 → 사용자 판단 필요 항목(2차 보고 시점까지 답변 없어 본표 유지). 법률 용어는 '품목제조보고'(보고)이고 인터뷰이는 '신고'로 표현함(검토메모 24). 사례는 서대문구 1건. 식품위생법 제48조 체계와의 세부 비교는 시행규칙 제62조만 확인하고 고시의 식품 부분은 미대조.</t>
         </is>
       </c>
     </row>
@@ -818,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -957,130 +913,130 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
+    <row r="6" ht="84" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>보완서류의 이메일 제출 거부·방문 보완 요구(담당 업무의 30~40%)</t>
+          <t>처리기간 산정 중지(보완기간 불산입) 미안내, 처리결과 미통지, 불허 사유 미제시</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>정은지(8.25): 정은지: "네. 저희가 이제 이메일로 보완하면 안 되겠냐라고 하면 절대 안 된다고 이렇게 하는 분도 있어요." / 정은지: "한 3-40% 정도요"</t>
+          <t>박정모(8.26): 박정모: "그다음에 처리기간 산정이 중지되는 것은 잘 안 알려줘요. 공무원들이 내부적으로 문제가 된 거는 공무원 특성상 잘 안 알려주고, 질의 회신이나 이런 게 늦어져도 그 이유도 잘 안 알려주세요."
+이종서(8.26): 이종서: "이것도 지자체에 따라 다르긴 한데 이게 결과가 나왔는지 안 나왔는지 통보를 안 해줍니다. 그러니까 그 날짜 되면 알아서 찾아가라는 경우가 있어요. 이걸 전화를 해서 확인을 해야 돼요." / 한시적 영업 불허 사유 '그 지역 안 된다'(본표 연번 3 인용 참조).</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>민원처리법 제8조(민원 신청은 전자문서 포함 문서로), 제22조(보완 요구), 시행령 제5조(직접 방문이 필요 없는 민원은 정보통신망·우편 신청 가능), 제24조①(보완 '요구'는 문서 또는 구술로) — 민원인의 보완서류 제출 방법은 명문 규정 없음. 신청이 전자문서로 가능하면 보완도 전자 제출이 가능하다는 해석이 통상적.</t>
+          <t>행정절차법 시행령 제11조1호·민원처리법 시행령 제20조1호(보완기간 등 불산입), 시행령 제23조(30일 경과 시 진행상황·완료 예정일 통지, 30일마다), 민원처리법 제27조①·③·시행령 제29조①(완료 시 지체 없이 통지, 거부 시 이유·구제절차), 행정절차법 제23조①(처분 이유 제시). 모두 명문 근거 있음.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>기준 2(해석으로 해결 가능). 부수 정비 검토 가능: 시행령 제24조에 '보완은 제5조의 방법으로 할 수 있다'를 명시하면 담당자 재량 여지 축소(행안부 소관).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="71" customHeight="1">
+          <t>기준 1. 보완 요구 시 불산입 사실의 안내는 본표 연번 2의 개정 방향 ②에 포함함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="97" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>처리기간 산정 중지(보완기간 불산입) 미안내, 처리결과 미통지, 불허 사유 미제시</t>
+          <t>사전심사 청구 제도의 활용 부진·사전상담 절차 법정화 요구</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>박정모(8.26): 박정모: "그다음에 처리기간 산정이 중지되는 것은 잘 안 알려줘요. 공무원들이 내부적으로 문제가 된 거는 공무원 특성상 잘 안 알려주고, 질의 회신이나 이런 게 늦어져도 그 이유도 잘 안 알려주세요."
-이종서(8.26): 결과 통보 없이 '날짜 되면 찾아가라'(연번 4 인용 참조), 한시적 영업 불허 사유 '그 지역 안 된다'(연번 2 인용 참조).</t>
+          <t>박정모(8.26): 박정모: "사전심사 제도는 있지만 이게 원활하게 활용이 안 돼 있다는 문제가 있어요."
+정은지(8.25): 정은지: "그리고 이제 사전 상담 제도 같은 게 좀 잘 되어 있으면 좋을 것 같아요. 어차피 사례집이 있어도 저희가 사전 상담은 무조건 필수적인 절차라서 이것들이 그냥 아예 절차로 좀 이렇게 규정이 되어 있는 게 차라리 낫지 않을까"</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>행정절차법 시행령 제11조1호·민원처리법 시행령 제20조1호(보완기간 등 불산입), 시행령 제23조(30일 경과 시 진행상황·완료 예정일 통지, 30일마다), 민원처리법 제27조①·③·시행령 제29조①(완료 시 지체 없이 통지, 거부 시 이유·구제절차), 행정절차법 제23조①(처분 이유 제시). 모두 명문 근거 있음.</t>
+          <t>민원처리법 제30조①(법정민원 중 대통령령으로 정하는 민원의 약식 사전심사 청구), ③(가능 통지 시 동일 결정 노력 의무), ④(제도 운영 장치 마련 의무). 시행령 제33조①: 대상 민원 = 토지매입 등 많은 비용이 수반되는 민원, 거부 시 상당한 경제적 손실이 발생하는 민원; ②: 행정기관장이 대상 민원 종류·처리기간·구비서류를 미리 정하여 게시·민원편람 수록. 제34조: 처리절차·구비서류 최소화·정식 접수 시 단축 처리.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>기준 1. 불산입 기간을 민원인에게 통지할 명문 의무는 없으나(시행령 제23조는 30일 경과 시), 보완 요구 시 '처리기간에 산입되지 않음'을 함께 안내하도록 시행령 제24조①에 추가하는 것은 부수 정비 검토 가능.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="71" customHeight="1">
+          <t>기준 1(제도 존재, 지자체가 대상 민원을 지정·게시하지 않으면 활용 불가한 운영 문제). 부수 정비 검토 가능: 임대차·시설투자가 선행되는 영업신고·등록을 시행령 제33조①에 예시로 추가(행안부 소관). 사전상담을 별도 법정 절차로 신설하는 것은 절차 추가로서 과제 범위 밖. 2차 보고 시점까지 격상 여부 답변 없어 검토메모 유지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>사전심사 청구 제도의 활용 부진·사전상담 절차 법정화 요구</t>
+          <t>폐기물 재활용 신고 시 건축물 용도(자원순환시설) 요구가 지역별로 상이, 환경부 질의회신으로 지자체 재량</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>박정모(8.26): 박정모: "사전심사 제도는 있지만 이게 원활하게 활용이 안 돼 있다는 문제가 있어요."
-정은지(8.25): 정은지: "그리고 이제 사전 상담 제도 같은 게 좀 잘 되어 있으면 좋을 것 같아요. 어차피 사례집이 있어도 저희가 사전 상담은 무조건 필수적인 절차라서 이것들이 그냥 아예 절차로 좀 이렇게 규정이 되어 있는 게 차라리 낫지 않을까"</t>
+          <t>이종서(8.26): 이종서: "어떤 분은 근린생활시설에서도 했고 어떤 분은 공장 건축물 용도에서도 했는데 어느 지역에서는 또 안 돼요. 그러니까 어느 지역에서는 무조건 자원 순환 시설이라고 얘기하는 경우가 있어요." / 이종서: "작년에 질의가 나왔던 게 자원순환시설 아니어도 지자체의 재량껏 그걸 준 거예요. 그러니까 더 혼란이 있는 거죠."</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>민원처리법 제30조①(법정민원 중 대통령령으로 정하는 민원의 약식 사전심사 청구), ③(가능 통지 시 동일 결정 노력 의무), ④(제도 운영 장치 마련 의무). 시행령 제33조①: 대상 민원 = 토지매입 등 많은 비용이 수반되는 민원, 거부 시 상당한 경제적 손실이 발생하는 민원; ②: 행정기관장이 대상 민원 종류·처리기간·구비서류를 미리 정하여 게시·민원편람 수록. 제34조: 처리절차·구비서류 최소화·정식 접수 시 단축 처리.</t>
+          <t>폐기물관리법 제46조①(기후에너지환경부령 기준의 시설·장비를 갖추어 신고), 시행규칙 제66조①·별표 17(개정 2017.10.19): 보관시설·재활용시설·차량 기준만 있고 건축물 용도 요건 없음. 건축물 용도는 건축법 시행령 별표 1(자원순환 관련 시설)에 따른 국토부 소관 사항(별표 1 원문 미대조). 인터뷰이가 언급한 환경부 질의회신은 미확인.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>기준 1(제도 존재, 지자체가 대상 민원을 지정·게시하지 않으면 활용 불가한 운영 문제). 부수 정비 검토 가능: 임대차·시설투자가 선행되는 영업신고·등록을 시행령 제33조①에 예시로 추가(행안부 소관). 사전상담을 별도 법정 절차로 신설하는 것은 절차 추가로서 과제 범위 밖.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
+          <t>기준 2(해석·질의회신으로 해결, 두 법령의 교차 적용 문제). 폐기물관리법령에 용도 요건을 넣는 방향은 규제 신설(기준 3). 지자체 간 편차 주장은 지역이 특정되지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="71" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>폐기물 재활용 신고 시 건축물 용도(자원순환시설) 요구가 지역별로 상이, 환경부 질의회신으로 지자체 재량</t>
+          <t>폐기물처리 신고(제46조)를 '허가'로 오인한 사실상 반려, 사업계획서 사전검토 기준 불명</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>이종서(8.26): 이종서: "어떤 분은 근린생활시설에서도 했고 어떤 분은 공장 건축물 용도에서도 했는데 어느 지역에서는 또 안 돼요. 그러니까 어느 지역에서는 무조건 자원 순환 시설이라고 얘기하는 경우가 있어요." / 이종서: "작년에 질의가 나왔던 게 자원순환시설 아니어도 지자체의 재량껏 그걸 준 거예요. 그러니까 더 혼란이 있는 거죠."</t>
+          <t>이종서(8.26): 이종서: "그런 기계 설비가 없으면 이거는 신고다라고 환경부에서 질의가 내려온 게 있는데 이게 공무원분들이 파악이 안 돼 있다 보니까, "폐기물은 그냥 허가인데?" 라고 생각해서 반려 비슷하게 하는 경우가 되게 많아요." / 이종서: "근데 이것도 모든 업종에 또 해당되는 게 아니에요. 대부분은 모든 서류를 다 임대차 계약서부터 해가지고 다 내야 되거든요. 근데 폐기물 인허가증은 일부 허가의 경우 그리고 이것도 지자체별로 달라요."</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>폐기물관리법 제46조①(기후에너지환경부령 기준의 시설·장비를 갖추어 신고), 시행규칙 제66조①·별표 17(개정 2017.10.19): 보관시설·재활용시설·차량 기준만 있고 건축물 용도 요건 없음. 건축물 용도는 건축법 시행령 별표 1(자원순환 관련 시설)에 따른 국토부 소관 사항(별표 1 원문 미대조). 인터뷰이가 언급한 환경부 질의회신은 미확인.</t>
+          <t>폐기물관리법 제46조①~④: 신고 대상·변경신고·20일 내 수리 여부 통지·간주(2017.4.18 신설) 명문. 제25조①·②: 폐기물처리업 허가 전 사업계획서 제출·적합 통보 제도, ⑰3호: 재활용업은 사업계획 절차를 거치지 않고 허가 신청 가능 → '일부 허가만 사전검토'는 법령 구조와 일치.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>기준 2(해석·질의회신으로 해결, 두 법령의 교차 적용 문제). 폐기물관리법령에 용도 요건을 넣는 방향은 규제 신설(기준 3). 지자체 간 편차 주장은 지역이 특정되지 않음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="71" customHeight="1">
+          <t>기준 1(법령 명확, 담당자 숙지 부족). 사업계획서 사전검토 범위는 법 제25조⑰로 설명됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>폐기물처리 신고(제46조)를 '허가'로 오인한 사실상 반려, 사업계획서 사전검토 기준 불명</t>
+          <t>신청 서식에 법령 준수사항 기재 요구, 첨부서류(차량 성적서 등) 미표기, 서식 미갱신</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>이종서(8.26): 이종서: "그런 기계 설비가 없으면 이거는 신고다라고 환경부에서 질의가 내려온 게 있는데 이게 공무원분들이 파악이 안 돼 있다 보니까, "폐기물은 그냥 허가인데?" 라고 생각해서 반려 비슷하게 하는 경우가 되게 많아요." / 이종서: "근데 이것도 모든 업종에 또 해당되는 게 아니에요. 대부분은 모든 서류를 다 임대차 계약서부터 해가지고 다 내야 되거든요. 근데 폐기물 인허가증은 일부 허가의 경우 그리고 이것도 지자체별로 달라요."</t>
+          <t>이종서(8.26): 이종서: "뭐 폐기물 인허가 쪽에 차량에 관한 성적서 이런 게 필요한 것들이 있는데 그런 것들이 표기가 안 돼 있는 경우가 많아요."</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>폐기물관리법 제46조①~④: 신고 대상·변경신고·20일 내 수리 여부 통지·간주(2017.4.18 신설) 명문. 제25조①·②: 폐기물처리업 허가 전 사업계획서 제출·적합 통보 제도, ⑰3호: 재활용업은 사업계획 절차를 거치지 않고 허가 신청 가능 → '일부 허가만 사전검토'는 법령 구조와 일치.</t>
+          <t>폐기물관리법 시행규칙 제67조①2호 첨부서류 7종, 별표 17 비고 3(차량은 별표 5 기준 적합) — 서식(별지 제56호의2)의 안내 문구는 미확인. 해당 발언은 주로 폐기물처리업 '허가' 사업계획서에 관한 것.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>기준 1(법령 명확, 담당자 숙지 부족). 사업계획서 사전검토 범위는 법 제25조⑰로 설명됨.</t>
+          <t>기준 1(서식 안내·운영). 허가 영역은 과제 범위 밖. 서식 안내 보강은 부수 정비.</t>
         </is>
       </c>
     </row>
@@ -1090,73 +1046,73 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>신청 서식에 법령 준수사항 기재 요구, 첨부서류(차량 성적서 등) 미표기, 서식 미갱신</t>
+          <t>처리결과 문서(공장등록증·허가증·신고증)의 방문 수령 요구, 전자 교부 거부</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>이종서(8.26): 이종서: "뭐 폐기물 인허가 쪽에 차량에 관한 성적서 이런 게 필요한 것들이 있는데 그런 것들이 표기가 안 돼 있는 경우가 많아요."</t>
+          <t>이범원(8.28): 이범원: "그걸 그냥 온라인으로 뿌려주면 좋은데 꼭 와서 갖고 가라." / 이범원: "저 허가증 같은 것도 와서 도장을 찍어 갖고 오라는 데가 있어요."</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>폐기물관리법 시행규칙 제67조①2호 첨부서류 7종, 별표 17 비고 3(차량은 별표 5 기준 적합) — 서식(별지 제56호의2)의 안내 문구는 미확인. 해당 발언은 주로 폐기물처리업 '허가' 사업계획서에 관한 것.</t>
+          <t>민원처리법 제27조①·②(전자민원 신청 시 전자문서 통지 갈음, 요청 시 문서 교부)·④, 시행령 제29조①(교부 또는 정보통신망·우편 통지), 전자정부법 제7조②(종이문서 통지 규정에도 전자문서 통지 가능). 산업집적법 제16조(공장등록대장 등록; 등록증 교부 방식은 산업통상부령 — 시행규칙 미확인).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>기준 1(서식 안내·운영). 허가 영역은 과제 범위 밖. 서식 안내 보강은 부수 정비.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t>기준 1. 공장등록증 서식의 교부 방식 조문은 미확인(산집법 시행규칙).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="71" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>처리결과 문서(공장등록증·허가증·신고증)의 방문 수령 요구, 전자 교부 거부</t>
+          <t>정부24 등 온라인 신고 접수 기피·방문 유도('갖고 오면 3일, 온라인은 일주일'), 담당자가 온라인 접수 절차를 모름</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>이범원(8.28): 이범원: "그걸 그냥 온라인으로 뿌려주면 좋은데 꼭 와서 갖고 가라." / 이범원: "저 허가증 같은 것도 와서 도장을 찍어 갖고 오라는 데가 있어요."</t>
+          <t>이범원(8.28): 이범원: "서류를 담당자도 모르는 경우도 있어요. 자기가 정부 24시에서 신고가 되면 접수를 해야 되는지도 모르는 분들도 있고" / 이범원: "쉽게 얘기해서 갖고 오면 3일 여기다 신청하면 일주일 이렇게 얘기를 해요."
+정은지(8.25): 정은지: "제가 초반에는 전화 안 하고 그냥 법령이랑 정부24 확인을 다 하고 갔는데 안 된 경우가 거의 100%였어요. 전화는 무조건 하고 지자체가 원하는 서류를 다 내야 돼요."</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>민원처리법 제27조①·②(전자민원 신청 시 전자문서 통지 갈음, 요청 시 문서 교부)·④, 시행령 제29조①(교부 또는 정보통신망·우편 통지), 전자정부법 제7조②(종이문서 통지 규정에도 전자문서 통지 가능). 산업집적법 제16조(공장등록대장 등록; 등록증 교부 방식은 산업통상부령 — 시행규칙 미확인).</t>
+          <t>민원처리법 제12조의2④(전자민원창구 신청은 소관 행정기관에 신청한 것으로 봄), 시행령 제5조·제6조⑧(전자민원창구 도달 후 8근무시간 내 접수)·제10조③2호, 전자정부법 제7조①·⑤(전자 신청 종류·절차 공표). 처리기간은 신청 경로와 무관(민원처리법 제17조·제19조).</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>기준 1. 공장등록증 서식의 교부 방식 조문은 미확인(산집법 시행규칙).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="71" customHeight="1">
+          <t>기준 1(시스템·운영). 박정모(8.26)도 온라인이 더 늦다는 체감 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>정부24 등 온라인 신고 접수 기피·방문 유도('갖고 오면 3일, 온라인은 일주일'), 담당자가 온라인 접수 절차를 모름</t>
+          <t>전자민원창구 발급 인감증명서를 행정기관 제출용으로 인정하지 않음</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>이범원(8.28): 이범원: "서류를 담당자도 모르는 경우도 있어요. 자기가 정부 24시에서 신고가 되면 접수를 해야 되는지도 모르는 분들도 있고" / 이범원: "쉽게 얘기해서 갖고 오면 3일 여기다 신청하면 일주일 이렇게 얘기를 해요."
-정은지(8.25): 정은지: "제가 초반에는 전화 안 하고 그냥 법령이랑 정부24 확인을 다 하고 갔는데 안 된 경우가 거의 100%였어요. 전화는 무조건 하고 지자체가 원하는 서류를 다 내야 돼요."</t>
+          <t>이범원(8.28): 이범원: "굳이 지금 이제 우리 인감도 도장 없이 가잖아요. 그거 그다음에 전자문서로 뛰는 인감증명서 인정 안 해주잖아요." / 이범원: "관공서에 내는 거는 안 된다고 돼 있어 그래요."</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>민원처리법 제12조의2④(전자민원창구 신청은 소관 행정기관에 신청한 것으로 봄), 시행령 제5조·제10조③2호, 전자정부법 제7조①·⑤(전자 신청 종류·절차 공표). 처리기간은 신청 경로와 무관(민원처리법 제17조·제19조).</t>
+          <t>인감증명법 시행령 제13조②5호(개정 2024.5.7): 전자민원창구로 전자문서 인감증명서를 발급받을 수 있는 범위 = 부동산·자동차 매도용이 아닌 용도 중 (가) 법원 제출용(송무·등기·공탁·집행), (나) 금융기관 제출용을 제외한 것 → 행정기관 제출용은 전자 발급 가능. ④3의2호(별지 제14호의2서식, 일반용지 출력 가능), ⑧(위·변조 방지·진위확인 조치), 제14조(발급사실 확인).</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>기준 1(시스템·운영). 박정모(8.26)도 온라인이 더 늦다는 체감 언급.</t>
+          <t>기준 1. 발언('관공서에 내는 거는 안 된다고 돼 있어')과 법령이 다름 — 기록. 법인 인감증명서(등기소 발급)에 관한 것이라면 별도 검토 필요하나 발언에서 특정되지 않음.</t>
         </is>
       </c>
     </row>
@@ -1166,22 +1122,22 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>전자민원창구 발급 인감증명서를 행정기관 제출용으로 인정하지 않음</t>
+          <t>식품제조업 영업소 이전 시 건축물 용도(소매업소→제조업소) 변경 요구를 둘러싼 건축과·위생과 견해 차이</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>이범원(8.28): 이범원: "굳이 지금 이제 우리 인감도 도장 없이 가잖아요. 그거 그다음에 전자문서로 뛰는 인감증명서 인정 안 해주잖아요." / 이범원: "관공서에 내는 거는 안 된다고 돼 있어 그래요."</t>
+          <t>박정모(8.26): 박정모: "바로 옆 건물로 이전을 했는데 하나는 용도가 제조업소로 돼 있어서 원래 하던 곳과 상관이 없었는데 여기는 소매업으로 돼 있는 거예요. 그랬을 때 건축과에서는 "이건 상관은 없다"라고 했죠." / 박정모: "그다음에 이거를 위생과에다 물어봤더니 위생과에서는 바꾸시라고 그렇게 얘기를 한 거예요."</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>인감증명법 시행령 제13조②5호(개정 2024.5.7): 전자민원창구로 전자문서 인감증명서를 발급받을 수 있는 범위 = 부동산·자동차 매도용이 아닌 용도 중 (가) 법원 제출용(송무·등기·공탁·집행), (나) 금융기관 제출용을 제외한 것 → 행정기관 제출용은 전자 발급 가능. ④3의2호(별지 제14호의2서식, 일반용지 출력 가능), ⑧(위·변조 방지·진위확인 조치), 제14조(발급사실 확인).</t>
+          <t>건축법 제19조③(같은 시설군 내 용도변경은 건축물대장 기재내용 변경 신청, 단서 대통령령으로 정하는 변경 제외), 시행령 제14조④2호(관계 법령 용도제한에 적합한 범위에서 제1종·제2종 근린생활시설 상호 간 변경은 신청 불요) → 건축과 의견과 부합. 식품위생법 시행규칙 별표 14 제1호(식품제조·가공업 시설기준)에 건축물 용도 요건 없음(작업장 분리 등만 규정).</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>기준 1. 발언('관공서에 내는 거는 안 된다고 돼 있어')과 법령이 다름 — 기록. 법인 인감증명서(등기소 발급)에 관한 것이라면 별도 검토 필요하나 발언에서 특정되지 않음.</t>
+          <t>기준 2(해석 차이, 부서 간 협의로 해결). 인천 남동구 1건.</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1147,22 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>식품제조업 영업소 이전 시 건축물 용도(소매업소→제조업소) 변경 요구를 둘러싼 건축과·위생과 견해 차이</t>
+          <t>옥외영업 신고 시 집합건물 관리주체·건물주 동의서 요구</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>박정모(8.26): 박정모: "바로 옆 건물로 이전을 했는데 하나는 용도가 제조업소로 돼 있어서 원래 하던 곳과 상관이 없었는데 여기는 소매업으로 돼 있는 거예요. 그랬을 때 건축과에서는 "이건 상관은 없다"라고 했죠." / 박정모: "그다음에 이거를 위생과에다 물어봤더니 위생과에서는 바꾸시라고 그렇게 얘기를 한 거예요."</t>
+          <t>이범원(8.28): 이범원: "그럼 그거를 허가를 받기 전에 신고를 하기 전에 건물에서 그거를 용인을 했느냐 건물주들이 관리사무소가 따로 그런 그런 것들의 접근성인가 뭐 그런 것들 때문에 이제 못하고 맡기시는 분들이 있어요." / 이범원: "그래서 이제 그런 거 가서 동의서 받아와라 그럴 때 이제 참"</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>건축법 제19조③(같은 시설군 내 용도변경은 건축물대장 기재내용 변경 신청, 단서 대통령령으로 정하는 변경 제외), 시행령 제14조④2호(관계 법령 용도제한에 적합한 범위에서 제1종·제2종 근린생활시설 상호 간 변경은 신청 불요) → 건축과 의견과 부합. 식품위생법 시행규칙 별표 14 제1호(식품제조·가공업 시설기준)에 건축물 용도 요건 없음(작업장 분리 등만 규정).</t>
+          <t>식품위생법 시행규칙 제42조①13호·제43조①2호: 외부 장소에 대한 '정당한 사용 권한이 있음을 증명하는 서류' — 집합건물 공용부분(대지)을 사용하는 경우 관리단·소유자 동의로 사용 권한을 증명하도록 하는 것은 문언의 해석 범위 내.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>기준 2(해석 차이, 부서 간 협의로 해결). 인천 남동구 1건.</t>
+          <t>기준 2. 본표 연번 1·5 및 검토메모 22와 동일 제도[교차확인]. 증명 서류의 예시(소유자·관리단 동의서, 임대차계약서 특약 등)를 서식 안내에 두는 것은 부수 정비.</t>
         </is>
       </c>
     </row>
@@ -1216,249 +1172,275 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>옥외영업 신고 시 집합건물 관리주체·건물주 동의서 요구</t>
+          <t>직접생산확인증명서 미보유 시 대체서류 안내 없이 반려</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>이범원(8.28): 이범원: "그럼 그거를 허가를 받기 전에 신고를 하기 전에 건물에서 그거를 용인을 했느냐 건물주들이 관리사무소가 따로 그런 그런 것들의 접근성인가 뭐 그런 것들 때문에 이제 못하고 맡기시는 분들이 있어요." / 이범원: "그래서 이제 그런 거 가서 동의서 받아와라 그럴 때 이제 참"</t>
+          <t>박정모(8.26): 박정모: "그래서 의뢰인이 그런 게 없다라고 했을 때 공무원이 그게 필요한데요라고 하면은 의뢰인은 그거를 대신할만 대체할 만한 서류를 제출을 해야 되는데 공무원은 그냥 반려만 딱 하고 마니까 의뢰인분들이 그걸 모르겠는 거죠."</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>식품위생법 시행규칙 제42조①13호·제43조①2호: 외부 장소에 대한 '정당한 사용 권한이 있음을 증명하는 서류' — 집합건물 공용부분(대지)을 사용하는 경우 관리단·소유자 동의로 사용 권한을 증명하도록 하는 것은 문언의 해석 범위 내.</t>
+          <t>중소기업제품 구매촉진 및 판로지원에 관한 법률 제9조(공공조달 계약 시 직접생산 확인, 중기부 발급 증명서). 공공조달·지자체 창업지원 영역으로 신고제도 범위 밖.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>기준 2. 본표 연번 1·4·5와 동일 제도[교차확인]. 증명 서류의 예시(소유자·관리단 동의서, 임대차계약서 특약 등)를 서식 안내에 두는 것은 부수 정비.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t>기준 3(범위 외). 대체서류 안내는 운영 사항.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>직접생산확인증명서 미보유 시 대체서류 안내 없이 반려</t>
+          <t>행정사 등 대리인의 전자민원 인증 수단 부재(홈택스·정부24 대리인 로그인 없음, 의뢰인 사업자용 범용 인증서 요구)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>박정모(8.26): 박정모: "그래서 의뢰인이 그런 게 없다라고 했을 때 공무원이 그게 필요한데요라고 하면은 의뢰인은 그거를 대신할만 대체할 만한 서류를 제출을 해야 되는데 공무원은 그냥 반려만 딱 하고 마니까 의뢰인분들이 그걸 모르겠는 거죠."</t>
+          <t>정은지(8.25): 정은지: "그 홈텍스 같은 데 저희는 아예 그게 없어요. 홈페이지에 접속할 수 있는 권한이 아예 없어요."
+박정모(8.26): 박정모: "왜냐하면 대개는 일반 공인인증서가 아니라 사업자용 범용 인증서를 요구하거든요. 사업자용 범용 인증서는 국세청부터 다 들어갈 수 있는데, 그거 불편해하시는 분들이 있어서요."</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>중소기업제품 구매촉진 및 판로지원에 관한 법률 제9조(공공조달 계약 시 직접생산 확인, 중기부 발급 증명서). 공공조달·지자체 창업지원 영역으로 신고제도 범위 밖.</t>
+          <t>행정사법 제2조①4호·5호(제출 대행, 신고 대리), 행정절차법 제12조①5호(법령에 따라 대리인이 될 수 있는 자), 전자정부법 제10조(전자서명 등으로 신원 확인). 대리인 자격으로 전자민원창구에 접속·신청하는 인증 체계는 시스템 구축 사항으로, 법령이 이를 금지하는 조문은 확인되지 않음.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>기준 3(범위 외). 대체서류 안내는 운영 사항.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
+          <t>기준 1(시스템). 두 인터뷰 교차로 수요는 확인되나 법령 흠결로 특정하기 어려움. 행안부(정부24)·국세청 협의 사항.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="97" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>행정사 등 대리인의 전자민원 인증 수단 부재(홈택스·정부24 대리인 로그인 없음, 의뢰인 사업자용 범용 인증서 요구)</t>
+          <t>출입국 관련: 창구 예약 수개월 대기, 대행기관 등록 후 전자민원 3개월 대기, 사무소 이전 시 ID 폐쇄·재발급, E-6 비자 불허 기준 비공개, 영주권 심사 장기화, 민간위탁 안내센터(1345) 오안내 책임</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>정은지(8.25): 정은지: "그 홈텍스 같은 데 저희는 아예 그게 없어요. 홈페이지에 접속할 수 있는 권한이 아예 없어요."
-박정모(8.26): 박정모: "왜냐하면 대개는 일반 공인인증서가 아니라 사업자용 범용 인증서를 요구하거든요. 사업자용 범용 인증서는 국세청부터 다 들어갈 수 있는데, 그거 불편해하시는 분들이 있어서요."</t>
+          <t>박정모(8.26): 박정모: "근데 대행 기관 등록하고 나서 3개월 있다가 해야 돼요. 그게 이해가 안 되는 거예요. 본인들 말로는 바쁘대요. 그래서 허가를 내주는 게 3개월이나 걸려요." / 박정모: "그런데 이 아이디를 폐쇄하고 새로 발급받아야 돼요. 다시 3개월 기다려야죠."
+이범원(8.28): 이범원: "안 되는 건 좋다고 하는데 이유를 모르겠어요. 그럼 기준을 설정해 줘야 될 거 아니에요?"</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>행정사법 제2조①4호·5호(제출 대행, 신고 대리), 행정절차법 제12조①5호(법령에 따라 대리인이 될 수 있는 자), 전자정부법 제10조(전자서명 등으로 신원 확인). 대리인 자격으로 전자민원창구에 접속·신청하는 인증 체계는 시스템 구축 사항으로, 법령이 이를 금지하는 조문은 확인되지 않음.</t>
+          <t>출입국관리법 제79조의2(대행기관 등록·표준절차). 출입국민원 대행기관 관리지침(법무부 고시 제2021-447호) 제25조①: '대행기관으로 등록 후 3개월이 지난 기관은 법무부 전자민원(hikorea.go.kr)을 대행할 수 있다' → 3개월 대기는 고시 문언으로 확인. 제12조①: 주소 변경 등은 15일 내 변경신고 — ID 폐쇄·재발급은 지침 본문에 없음(운영). 체류 허가·비자는 허가 성격이며 법무부 소관.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>기준 1(시스템). 두 인터뷰 교차로 수요는 확인되나 법령 흠결로 특정하기 어려움. 행안부(정부24)·국세청 협의 사항.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="97" customHeight="1">
+          <t>기준 3(신고제도 범위 외 — 면담자도 '법제처 과제라서' 범위 외임을 언급). 3개월 대기(고시)와 ID 재발급(운영)은 법무부 협의 시 참고 자료로만 제시. 행정심판까지 간 E-6 사례는 허가 영역.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>출입국 관련: 창구 예약 수개월 대기, 대행기관 등록 후 전자민원 3개월 대기, 사무소 이전 시 ID 폐쇄·재발급, E-6 비자 불허 기준 비공개, 영주권 심사 장기화, 민간위탁 안내센터(1345) 오안내 책임</t>
+          <t>규제 강화·신설 또는 규제 수준 자체에 관한 의견</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>박정모(8.26): 박정모: "근데 대행 기관 등록하고 나서 3개월 있다가 해야 돼요. 그게 이해가 안 되는 거예요. 본인들 말로는 바쁘대요. 그래서 허가를 내주는 게 3개월이나 걸려요." / 박정모: "그런데 이 아이디를 폐쇄하고 새로 발급받아야 돼요. 다시 3개월 기다려야죠."
-이범원(8.28): 이범원: "안 되는 건 좋다고 하는데 이유를 모르겠어요. 그럼 기준을 설정해 줘야 될 거 아니에요?"</t>
+          <t>이범원: 축산물 HACCP 전면 의무화 비용(기준서 100페이지, 설치비 1억). 정은지: 식육포장처리업 HACCP 의무화로 1인 사업자 부담. 이종서: 동물보호법 강화로 애견카페 인허가 까다로움, 가축사육업 50㎡ 기준. 박정모: 영업정지 기간 단축(7일~1개월→3~7일) 비판, 제재 필요. 박정모·이범원: 무자격 대행업체 광고 제재·행정사법 준수 계도 요구.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>출입국관리법 제79조의2(대행기관 등록·표준절차). 출입국민원 대행기관 관리지침(법무부 고시 제2021-447호) 제25조①: '대행기관으로 등록 후 3개월이 지난 기관은 법무부 전자민원(hikorea.go.kr)을 대행할 수 있다' → 3개월 대기는 고시 문언으로 확인. 제12조①: 주소 변경 등은 15일 내 변경신고 — ID 폐쇄·재발급은 지침 본문에 없음(운영). 체류 허가·비자는 허가 성격이며 법무부 소관.</t>
+          <t>축산물 위생관리법 제9조③·시행규칙 제7조③(2024.1.12), 동물보호법·축산법 등은 미대조.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>기준 3(신고제도 범위 외 — 면담자도 '법제처 과제라서' 범위 외임을 언급). 3개월 대기(고시)와 ID 재발급(운영)은 법무부 협의 시 참고 자료로만 제시. 행정심판까지 간 E-6 사례는 허가 영역.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
+          <t>기준 3(규제의 실체적 수준·제재 신설·타 직역 규제). 본표 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>규제 강화·신설 또는 규제 수준 자체에 관한 의견</t>
+          <t>담당자 역량·순환보직·지침 미숙지, 담당자 부재 시 접수 불가, 매뉴얼 부재, 담당자 교육 요구</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>이범원: 축산물 HACCP 전면 의무화 비용(기준서 100페이지, 설치비 1억). 정은지: 식육포장처리업 HACCP 의무화로 1인 사업자 부담. 이종서: 동물보호법 강화로 애견카페 인허가 까다로움, 가축사육업 50㎡ 기준. 박정모: 영업정지 기간 단축(7일~1개월→3~7일) 비판, 제재 필요. 박정모·이범원: 무자격 대행업체 광고 제재·행정사법 준수 계도 요구.</t>
+          <t>이종서: 담당자 부재 시 신고인이 제출 못하고 돌아옴. 박정모: 보직 재직기간에 따른 역량 차이, 매뉴얼 없으면 '된다/안 된다' 갈림. 이범원: 2년 로테이션으로 숙지 안 됨, 통일 매뉴얼 부재. 정은지: 1순위 대안은 담당자 교육.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>축산물 위생관리법 제9조③·시행규칙 제7조③(2024.1.12), 동물보호법·축산법 등은 미대조.</t>
+          <t>민원처리법 시행령 제21조②(신설 2026.5.6): 단순 업무과중·담당자 지정 지연 또는 부재를 사유로 처리기간 연장 금지. 제22조 처리상황 확인·점검.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>기준 3(규제의 실체적 수준·제재 신설·타 직역 규제). 본표 제외.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t>기준 1(운영). 2026.5.6 신설 조항이 담당자 부재 문제를 직접 다루므로 운영 개선 근거로 활용 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="71" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>담당자 역량·순환보직·지침 미숙지, 담당자 부재 시 접수 불가, 매뉴얼 부재, 담당자 교육 요구</t>
+          <t>제도 개선 대안에 대한 인터뷰이 평가(정책 의견)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>이종서: 담당자 부재 시 신고인이 제출 못하고 돌아옴. 박정모: 보직 재직기간에 따른 역량 차이, 매뉴얼 없으면 '된다/안 된다' 갈림. 이범원: 2년 로테이션으로 숙지 안 됨, 통일 매뉴얼 부재. 정은지: 1순위 대안은 담당자 교육.</t>
+          <t>수리 폐지 반대(박정모 '있어야 된다'), 수리 간주는 신고증 발급이 필요하면 실효성 없음(박정모), 사후점검 전환은 식품·금융 등 피해자 발생 분야에는 부적절(정은지·박정모·이종서), 경미·중요 변경 분리는 연관성 때문에 혼란 우려(이종서) 또는 원스톱 선호(박정모), 온라인 신고 확대 찬성(전원), 반려 사유는 고시 이상·보완 사항은 가이드라인으로 계층화(박정모), 외국인환자 유치업 정기보고 시스템은 좋은 사례(정은지), 온라인 법인설립시스템·HACCP 단계별 안내는 좋은 사례(이범원·이종서).</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>민원처리법 시행령 제21조②(신설 2026.5.6): 단순 업무과중·담당자 지정 지연 또는 부재를 사유로 처리기간 연장 금지. 제22조 처리상황 확인·점검.</t>
+          <t>행정규제기본법 제4조(규제 법정주의)는 '반려 사유는 고시 이상' 제안의 법적 근거가 될 수 있으나 특정 제도가 지목되지 않음.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>기준 1(운영). 2026.5.6 신설 조항이 담당자 부재 문제를 직접 다루므로 운영 개선 근거로 활용 가능.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="71" customHeight="1">
+          <t>기준 2·3(정책 사항·일반론). 연구진 대안 평가 자료로만 활용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>제도 개선 대안에 대한 인터뷰이 평가(정책 의견)</t>
+          <t>사례 없음·추론 보류 항목</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>수리 폐지 반대(박정모 '있어야 된다'), 수리 간주는 신고증 발급이 필요하면 실효성 없음(박정모), 사후점검 전환은 식품·금융 등 피해자 발생 분야에는 부적절(정은지·박정모·이종서), 경미·중요 변경 분리는 연관성 때문에 혼란 우려(이종서) 또는 원스톱 선호(박정모), 온라인 신고 확대 찬성(전원), 반려 사유는 고시 이상·보완 사항은 가이드라인으로 계층화(박정모), 외국인환자 유치업 정기보고 시스템은 좋은 사례(정은지), 온라인 법인설립시스템·HACCP 단계별 안내는 좋은 사례(이범원·이종서).</t>
+          <t>정은지: 현장 실사를 생략할 수 있는 조항이 코로나 때 생겼다는 언급 — 어느 법령인지 특정되지 않음. 이종서: 중복 제출 '크게 없음', 공무원과의 분쟁 사례 '거의 없음'. 이범원: 신고 지연으로 사업 착수가 지연되는 것은 '신청인의 실수'. 박정모: 폐업 신고 의뢰는 거의 없음.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>행정규제기본법 제4조(규제 법정주의)는 '반려 사유는 고시 이상' 제안의 법적 근거가 될 수 있으나 특정 제도가 지목되지 않음.</t>
+          <t>해당 없음(미확인).</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>기준 2·3(정책 사항·일반론). 연구진 대안 평가 자료로만 활용.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t>입법사실 없음 → 제외. 발언을 추론으로 메우지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="136" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>사례 없음·추론 보류 항목</t>
+          <t>[1차 본표 4 → 제외] 옥외영업 변경신고의 사전 현장 확인·유관부서 확인과 결과 미통보</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>정은지: 현장 실사를 생략할 수 있는 조항이 코로나 때 생겼다는 언급 — 어느 법령인지 특정되지 않음. 이종서: 중복 제출 '크게 없음', 공무원과의 분쟁 사례 '거의 없음'. 이범원: 신고 지연으로 사업 착수가 지연되는 것은 '신청인의 실수'. 박정모: 폐업 신고 의뢰는 거의 없음.</t>
+          <t>이종서(8.26): 보완 요구의 대표 사례가 옥외영업(테라스) 신고로, 도로법 등 유관 부서가 관련되어 사전 확인이 어렵고 '나와서 봐야 알 수 있다'며 현장 확인 뒤 통행로 폭 등으로 보완을 요구함.
+이종서: "어쩔 수 없이 뭐 나온다고 하면은 유관 부서와 관련된 건들 그리고 예를 들면은 옥외영업 신고라는 게 있거든요. 그러니까 테라스 밖에서 이제 음식 이렇게 하고 이런 것들 있지 않습니까? 이런 것들도 도로법부터 해가지고 여러 가지 유관 부서가 있다 보니까 모든 거는 체크하기 어려운 경우가 있거든요. 그리고 미리 얘기해 주지 않는 경우가 있죠." / 이종서: "일단 우리가 나와서 봐야 알 수 있다라고 하기 때문에 도면으로 보는 것과 실제로 나갔을 때 그게 다른 경우가 있을 수 있거든요. 그런 것들이 보완이 올 수가 있죠. 예를 들면은 여기 통행로가 도면상으로는 5m인데 실제로 나가 보니까 한 4점 몇 미터가 측정이 됐다든가. 그렇게 되면은 의자를 조금 더 치워가지고 통로를 확보를 하고 이런 것들인 거죠. 굳이 따지자면 그런 것들이 있고 서류적인 보완은 그렇게 크게 있진 않아요."</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>해당 없음(미확인).</t>
+          <t>식품위생법 제37조④·⑫·⑬, 시행규칙 제42조⑧·⑩(신규 신고는 신고증 발급 후 15일/1개월 내 시설 확인), 제43조(변경신고에 신고증 발급·사후확인 조항 없음), 별표 14 제8호나목1)사), 별지 제41호서식(처리절차 '신고증 발급→필요시 시설조사 15일 이내'). 민원처리법 시행령 제21조①2호(현장 확인 필요 시 처리기간 연장·문서 통지).</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>입법사실 없음 → 제외. 발언을 추론으로 메우지 않음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="136" customHeight="1">
+          <t>1차 본표(연번 4)에 수록했으나 2026.10.15 사용자 판단으로 본표 제외. 조문-서식 불일치(제43조 사후확인 근거 부재)는 본표 연번 1·5의 개정 방향 ①에 이미 포함됨. 통행로 폭 등 수치 기준을 별표에 명시하는 방향은 규제 신설 소지(기준 3)로 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="84" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>인터뷰이 발언과 법령·용어의 차이 기록(발언은 수정하지 않음)</t>
+          <t>[1차 본표 6 → 제외] 행정사 업무신고 처리기간(10일)과 수리 간주 기간(3개월)의 괴리</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>(a) 이종서: 한시적 영업신고에 '상위법에도 규정이 없다' → 식품위생법 시행규칙 제42조③·별표 14 제8호가목5)에 규정 있음(민간 행사는 지자체장 '별도 지정'에 위임). (b) 이종서: 사업자등록증이 공동이용에서 빠져 있다 → 농지법 시행규칙 제7조④7호 등에 공동이용 서류로 명시. (c) 이범원: 전자 인감증명서는 관공서 제출 불가로 되어 있다 → 인감증명법 시행령 제13조②5호는 법원·금융기관 제출용만 제외. (d) 정은지: 농지취득자격증명 '면담 재량 조항' → 법·령·규칙·예규에서 미확인. (e) 박정모: 행정사 '영업신고' → 법률 용어 '업무신고'(행정사법 제10조). (f) 이범원: 품목제조보고를 '신고' → 법률 용어 '보고'(축산물 위생관리법 제25조). (g) 이종서: '신고는 7일 이내 수리, 허가는 15일' → 제도별 상이(식품위생법 신고 3일·서식 즉시, 폐기물 신고 20일, 행정사 업무신고 10일 등). (h) 이범원: 축산물가공업 '등록 관청에다가 허가를 등록' → 법률상 시·도지사 허가(제22조①).</t>
+          <t>박정모(8.26): 박정모: "행정사의 영업신고는 10일이 잡혀 있거든요? 근데 각 지역마다 3일 만에 해 주는 데가 있고 보름 만에 해 주는 데가 있어요." / 박정모: "한국인한테 비슷한 예로, 제가 올해 초에 동기들과 영업 신고를 했는데 종로구는 3일 만에 나오더라고요. 근데 여기 은평구는 일주일이 넘었는데도 연락이 없어요. 그래서 전화를 해봤어요. 그랬더니 지금 오시면 바로 준대요."</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>각 조문은 참조 시트 참조.</t>
+          <t>행정사법 제10조①(업무신고), 제11조①(기준 미달 시 수리 거부·사유 통지)·②(개정 2020.6.9: '업무신고를 받은 날부터 3개월이 지날 때까지' 확인증 미발급·거부 미통지 시 3개월이 되는 날의 다음 날 수리 간주), 제12조①(확인증 발급). 시행령 제20조①(기준 4개: 결격사유·실무교육·자격증·행정사회 가입), ③(행정사정보시스템 확인, 신설 2025.10.10). 시행규칙 별지 제8호서식(개정 2025.11.20) 처리기간 10일. 서식 처리기간과 법률 간주 기간의 불일치는 문언으로 확인됨(법제처 신고 정비 표준인 '처리기간 종료일 다음 날 간주'와 다름).</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>검토메모 기록용.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="110" customHeight="1">
+          <t>1차 본표(연번 6)에 수록했으나 2026.10.15 사용자 판단으로 본표 제외(행정안전부 소관 법률이고 인터뷰이가 행정사 본인인 이해관계자 진술). 인터뷰이 표현 '영업신고'는 법률 용어 '업무신고'. 2020.6.9 개정 이유는 원문 미대조. 필요 시 별도 과제(행정사법 정비)에서 검토 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="162" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>인터뷰이 발언과 법령·용어의 차이 기록(발언은 수정하지 않음)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>(a) 이종서: 한시적 영업신고에 '상위법에도 규정이 없다' → 식품위생법 시행규칙 제42조③·별표 14 제8호가목5)에 규정 있음(민간 행사는 지자체장 '별도 지정'에 위임). (b) 이종서: 사업자등록증이 공동이용에서 빠져 있다 → 농지법 시행규칙 제7조④7호 등에 공동이용 서류로 명시. (c) 이범원: 전자 인감증명서는 관공서 제출 불가로 되어 있다 → 인감증명법 시행령 제13조②5호는 법원·금융기관 제출용만 제외. (d) 정은지: 농지취득자격증명 '면담 재량 조항' → 법·령·규칙·예규에서 미확인. (e) 박정모: 행정사 '영업신고' → 법률 용어 '업무신고'(행정사법 제10조, 검토메모 23). (f) 이범원: 품목제조보고를 '신고' → 법률 용어 '보고'(축산물 위생관리법 제25조). (g) 이종서: '신고는 7일 이내 수리, 허가는 15일' → 제도별 상이(식품위생법 신고 3일·서식 즉시, 폐기물 신고 20일, 행정사 업무신고 10일 등). (h) 이범원: 축산물가공업 '등록 관청에다가 허가를 등록' → 법률상 시·도지사 허가(제22조①). (i) 정은지: 보완서류 이메일 제출은 담당자 '재량' → 민원처리법 제8조의2①은 구비서류의 전자 제출을 민원인의 권리로 규정(예외는 시행령 제5조의2).</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>각 조문은 참조 시트 참조.</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>검토메모 기록용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="149" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>제외 쟁점 요약(4절 기준별)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>기준 1(운영·시스템 문제): 공동이용 미이행, 온라인 접수 기피·방문 유도, 농지취득자격증명 방문 요구, 여행업 보증보험 선요구, 보완 방문 요구, 결과 미통지·사유 미제시, 사전심사 미활용, 폐기물 신고를 허가로 오인, 서식 안내 부족, 처리결과 문서 방문 수령, 전자 인감증명서 불인정, 대리인 전자인증 부재, 담당자 부재·역량. 기준 2(해석·지침으로 해결): 폐기물 재활용 신고의 건축물 용도, 식품제조업 용도변경 부서 간 견해, 옥외영업 집합건물 동의서, 가이드라인 계층화 일반론, 대안 평가 의견. 기준 3(범위 외·규제 신설): 출입국(체류 허가·대행기관 전자민원·안내센터), 직접생산확인(공공조달), HACCP·동물보호법·가축사육 규제 수준, 영업정지 기간, 무자격 대행 제재·행정사법 계도, 아파트 입주자대표회의 포상 규정(공동주택관리법, 신고 아님), 공장등록 후 확인(문제 제기 아님).</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>기준 1(운영·시스템 문제): 공동이용 미이행, 온라인 접수 기피·방문 유도, 농지취득자격증명 방문 요구, 여행업 보증보험 선요구, 결과 미통지·사유 미제시, 사전심사 미활용, 폐기물 신고를 허가로 오인, 서식 안내 부족, 처리결과 문서 방문 수령, 전자 인감증명서 불인정, 대리인 전자인증 부재, 담당자 부재·역량. 기준 2(해석·지침으로 해결): 폐기물 재활용 신고의 건축물 용도, 식품제조업 용도변경 부서 간 견해, 옥외영업 집합건물 동의서, 가이드라인 계층화 일반론, 대안 평가 의견. 기준 3(범위 외·규제 신설): 출입국(체류 허가·대행기관 전자민원·안내센터), 직접생산확인(공공조달), HACCP·동물보호법·가축사육 규제 수준, 영업정지 기간, 무자격 대행 제재·행정사법 계도, 아파트 입주자대표회의 포상 규정(공동주택관리법, 신고 아님), 공장등록 후 확인(문제 제기 아님). 사용자 판단으로 본표 제외(2026.10.15): 옥외영업 사전 현장확인(이종서, 검토메모 22), 행정사 업무신고 간주기간(박정모, 검토메모 23). 반대로 보완서류 전자 제출(정은지)은 1차 검토메모에서 본표 연번 2로 격상.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>본표 7건 외 쟁점은 모두 여기에 사유를 남김.</t>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>본표 6건 외 쟁점은 모두 여기에 사유를 남김.</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1663,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>제2조, 제10조, 제11조(② 3개월 수리 간주, 개정 2020.6.9), 제12조 원문 확인. 2020.6.9 개정 이유는 미대조.</t>
+          <t>제2조, 제10조, 제11조(② 3개월 수리 간주, 개정 2020.6.9), 제12조 원문 확인. 2020.6.9 개정 이유는 미대조. (2026.10.15 사용자 판단으로 본표 제외, 검토메모로 이동)</t>
         </is>
       </c>
     </row>
@@ -1817,11 +1799,11 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>제8조, 제9조, 제10조, 제12조의2, 제13조, 제17조, 제19조, 제22조, 제27조, 제30조 원문 확인.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
+          <t>제8조, 제8조의2(구비서류의 전자적 제출 — 2026.10.15 추가 확인), 제9조, 제10조, 제12조의2, 제13조, 제17조, 제19조, 제22조, 제27조, 제30조 원문 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>민원 처리에 관한 법률 시행령</t>
@@ -1834,7 +1816,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>목차 확인, 제5조, 제7조의2, 제10조, 제20조, 제21조(② 담당자 부재 사유 연장 금지 신설 2026.5.6), 제23조, 제24조, 제25조, 제29조, 제33조, 제34조 원문 확인.</t>
+          <t>목차 확인, 제5조, 제5조의2(전자적 제출의 예외)·제5조의3(전자화문서 진본성)·제6조(접수, ⑧ 전자민원창구 8근무시간 내 접수) — 2026.10.15 추가 확인, 제7조의2, 제10조, 제20조, 제21조(② 담당자 부재 사유 연장 금지 신설 2026.5.6), 제23조, 제24조, 제25조, 제29조, 제33조, 제34조 원문 확인.</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1833,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>법 제12조, 제23조, 제40조; 시행령 제11조 원문 확인.</t>
+          <t>법 제12조, 제17조(처분의 신청·보완 — 2026.10.15 추가 확인), 제23조, 제40조; 시행령 제11조 원문 확인.</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2071,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>DNS 차단으로 직접 접속 불가. 모든 조문은 korean-law MCP(Open API)로 확인. 사용자 원문 재확인 권장 항목은 채팅 보고 참조.</t>
+          <t>DNS 차단으로 직접 접속 불가. 모든 조문은 korean-law MCP(Open API)로 확인. 사용자 원문 재확인 권장 항목은 notes/questions.md 참조.</t>
         </is>
       </c>
     </row>

--- a/신고제도_행정사인터뷰/output/261014_입법영향분석_신고제도_행정사인터뷰_법령개정_필요사항.xlsx
+++ b/신고제도_행정사인터뷰/output/261014_입법영향분석_신고제도_행정사인터뷰_법령개정_필요사항.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="279" customHeight="1">
+    <row r="2" ht="292" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -524,7 +524,7 @@
         <is>
           <t>식품위생법 제37조제4항·제12항·제13항(제12항·제13항 신설 2018.12.11)
 식품위생법 시행령 제26조제4호
-식품위생법 시행규칙 제42조제1항제13호·제2항, 제43조제1항제2호(제1항 신설 2021.12.30, 개정 2026.9.1)·제2항, 별표 14 제8호나목1)사), 별지 제41호서식
+식품위생법 시행규칙 제42조제1항제13호(신설 2020.12.31, 시행 2021.1.1)·제2항, 제43조제1항제2호(제1항 신설 2021.12.30, 개정 2026.9.1)·제2항, 별표 14 제8호나목1)사), 별지 제41호서식
 민원 처리에 관한 법률 제9조제1항·제27조제3항, 같은 법 시행령 제21조제1항·제3항
 행정기본법 제34조, 행정절차법 제40조제1항, 행정규제기본법 제4조</t>
         </is>
@@ -537,11 +537,11 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>[현행 규정] 식품위생법 제37조④: 일반음식점 등 영업신고 및 중요사항 변경신고. ⑫: 신고·변경신고를 받은 날부터 3일 이내 수리 여부 통지(신설 2018.12.11, 제2호가 '제4항에 따른 영업신고 또는 변경신고' 명시). ⑬: 기간 내 미통지 시 기간이 끝난 날의 다음 날 수리 간주(신설 2018.12.11). 시행령 제26조제4호: 변경신고 사항 '영업장의 면적'. 시행규칙 제43조①2호(제1항 신설 2021.12.30, 개정 2026.9.1): 건물 외부의 연접 장소를 영업장으로 쓰기 위한 면적 변경신고 시 '사용하려는 장소에 대한 정당한 사용 권한이 있음을 증명하는 서류' 첨부, ②: 토지이용계획확인서·건축물대장 등은 신고관청이 공동이용으로 확인. 별표 14 제8호나목1)사): 건물 외부 영업장에는 '「건축법」 등 관계 법령에서 정하는 바에 따라 필요한 시설ㆍ설비 또는 기구 등을 설치해야 한다'. 별지 제41호서식: 처리기간 '즉시', 처리절차 '접수→서류검토→결재→신고증 발급→필요시 시설조사(15일 이내)'. 민원처리법 시행령 제21조①: 관계 기관·부서 협조, 현장 확인이 필요한 경우 처리기간 범위에서 1회 연장, ③: 연장 사유·처리완료 예정일을 문서로 통지.
+          <t>[현행 규정] 식품위생법 제37조④: 일반음식점 등 영업신고 및 중요사항 변경신고. ⑫: 신고·변경신고를 받은 날부터 3일 이내 수리 여부 통지(신설 2018.12.11, 제2호가 '제4항에 따른 영업신고 또는 변경신고' 명시). ⑬: 기간 내 미통지 시 기간이 끝난 날의 다음 날 수리 간주(신설 2018.12.11). 시행령 제26조제4호: 변경신고 사항 '영업장의 면적'. 시행규칙 제42조①13호(총리령 제1661호, 2020.12.31 공포·2021.1.1 시행으로 신설): 영업장과 연접하는 외부 장소를 영업장으로 사용하려는 경우 '정당한 사용 권한이 있음을 증명하는 서류'. 제43조: 같은 개정으로 건물 외부 영업장 면적 변경 시 제13호 서류 첨부를 반영, 2021.12.30 개정(총리령 제1774호)으로 ①(변경 유형별 서류: 2호 '사용하려는 장소에 대한 정당한 사용 권한이 있음을 증명하는 서류')·②(토지이용계획확인서·건축물대장 등 공동이용 확인)으로 재편, 2026.9.1 개정으로 ①의 영업신고증 첨부 문구 삭제(이상 연혁은 사용자 제공 신구조문대비표로 확인). 별표 14 제8호나목1)사): 건물 외부 영업장에는 '「건축법」 등 관계 법령에서 정하는 바에 따라 필요한 시설ㆍ설비 또는 기구 등을 설치해야 한다'. 별지 제41호서식: 처리기간 '즉시', 처리절차 '접수→서류검토→결재→신고증 발급→필요시 시설조사(15일 이내)'. 민원처리법 시행령 제21조①: 관계 기관·부서 협조, 현장 확인이 필요한 경우 처리기간 범위에서 1회 연장, ③: 연장 사유·처리완료 예정일을 문서로 통지.
 [문제점] ① 법령은 옥외영업을 '영업장 면적 변경신고'로 설계해 즉시 처리·3일 내 수리 통지·미통지 시 간주, 시설 확인은 신고증 발급 후 사후 조사로 정했는데, 실무는 사전 협의→현장 방문→다른 기관 협의 뒤 수리 여부를 정하고 '보류' 상태로 두어 법 제37조⑬의 간주 효과와 충돌함(법률상 이미 수리로 간주된 신고를 행정청이 미수리로 취급). ② '법령 해석·다른 기관 협의'가 필요하면 민원처리법 시행령 제21조에 따라 연장 사유와 예정일을 문서로 통지해야 하나, 식품위생법령에는 옥외영업 변경신고에서 별표 14 제8호나목1)사)의 '관계 법령' 적합 여부를 신고인이 책임지는 준수사항으로 보는지 신고관청의 심사사항으로 보는지 규정이 없어, 심사사항으로 해석하는 지자체에서는 3일 처리기간과 구조적으로 양립할 수 없음. ③ 그 결과 별표 14의 요건 외 사유(제3자 민원, 타 부서 의견)로 수리가 지연·거부되는 경로가 열려 있고, 인터뷰이는 조문상 요건을 모두 확인하고도 결과를 예측할 수 없다고 진술.
 [논거] 행정기본법 제34조: 수리가 필요한 신고는 법률에 명시된 경우에 한하며, 식품위생법 제37조⑬은 기간 경과 시 수리 간주를 명시하므로 간주 이후의 '보류'는 법률상 근거가 없음. 행정절차법 제40조①·민원처리법 제13조: 신고 요건과 심사기준은 미리 게시해야 하므로, 법령에 특정되지 않은 '관계 법령 적합성'을 수리 요건처럼 운용하는 것은 규제 법정주의(행정규제기본법 제4조)와 예측가능성에 반함. 민원처리법 제9조①(접수 보류·거부 금지), 제27조③(거부 시 이유·구제절차 통지).
-[개정 방향] ① (시행규칙 제43조) 변경신고, 특히 영업장 면적 변경신고의 처리에 제42조⑧(신고증 발급)·⑩(발급 후 15일 이내 시설 확인)을 준용하는 항을 신설하여 '선수리·후확인' 구조를 서식이 아닌 조문에 명시. ② (시행규칙 별표 14 제8호나목1)사)) 옥외영업장 요건 중 신고관청이 확인하는 사항(예: 건축물대장상 대지 범위 내 여부, 도로 점용 여부)과 영업자 준수사항으로 두는 사항을 구분해 명시하고, 다른 법령 적합성 확인이 필요한 경우 민원처리법 시행령 제21조의 연장 통지 절차를 따르도록 규칙에 명시. ③ (법률) 제37조⑬ 간주 이후 신고증(변경사항 기재) 교부 의무를 시행규칙 제43조에 함께 신설하여 간주의 실효성 확보(연번 5와 연계). 법률 개정 없이 ①·②는 시행규칙만으로 가능.
-[유의] 식약처 소관. 2021.12.30·2026.9.1 시행규칙 개정으로 옥외영업 조문이 최근 바뀌어 개정 전후 신구대조는 원문 미대조. 인터뷰이 사례는 2026년 인천 연수구 1건으로 입법사실 규모는 제한적이나, 4개 인터뷰 모두 옥외영업 신고를 '허가처럼 운영되는' 대표 사례로 지목. 경쟁업체 민원 영향은 인터뷰이 추정. 옥외영업 허용 요건 자체를 추가하는 방향은 규제 강화로 과제 범위 밖. [교차확인] 연번 5(박정모 인터뷰)와 동일 쟁점. 검토메모 22(이종서 인터뷰, 사용자 판단으로 본표 제외)·14(이범원 인터뷰) 참조.</t>
+[개정 방향] ① (시행규칙 제43조) 변경신고, 특히 영업장 면적 변경신고의 처리에 제42조⑧(신고증 발급)·⑩(발급 후 15일 이내 시설 확인)을 준용하는 항을 신설하여 '선수리·후확인' 구조를 서식이 아닌 조문에 명시. ② (시행규칙 별표 14 제8호나목1)사)) 옥외영업장 요건 중 신고관청이 확인하는 사항(예: 건축물대장상 대지 범위 내 여부, 도로 점용 여부)과 영업자 준수사항으로 두는 사항을 구분해 명시하고, 다른 법령 적합성 확인이 필요한 경우 민원처리법 시행령 제21조의 연장 통지 절차를 따르도록 규칙에 명시. ③ (법률) 제37조⑬ 간주 이후 신고증(변경사항 기재) 교부 의무를 시행규칙 제43조에 함께 신설하여 간주의 실효성 확보(연번 4와 연계). 법률 개정 없이 ①·②는 시행규칙만으로 가능.
+[유의] 식약처 소관. 제42조·제43조의 옥외영업 관련 연혁은 사용자 제공 신구조문대비표(총리령 제1661호·제1774호)로 확인했으나, 별표 14 제8호나목1)사)(건물 외부 영업장 안전시설)의 신설 시점은 미대조. 인터뷰이 사례는 2026년 인천 연수구 1건으로 입법사실 규모는 제한적이나, 4개 인터뷰 모두 옥외영업 신고를 '허가처럼 운영되는' 대표 사례로 지목. 경쟁업체 민원 영향은 인터뷰이 추정. 옥외영업 허용 요건 자체를 추가하는 방향은 규제 강화로 과제 범위 밖. [교차확인] 연번 4(박정모 인터뷰)와 동일 쟁점. 검토메모 22(이종서 인터뷰, 사용자 판단으로 본표 제외)·14(이범원 인터뷰) 참조.</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>민원 처리에 관한 법률 제8조, 제8조의2제1항, 제12조의2제1항, 제22조제1항·제3항
+          <t>민원 처리에 관한 법률 제8조, 제8조의2제1항(신설 2022.1.11, 법률 제18698호), 제12조의2제1항, 제22조제1항·제3항
 민원 처리에 관한 법률 시행령 제5조, 제5조의2제1항·제2항, 제6조제8항, 제24조제1항~제4항
 행정절차법 제17조제5항, 제40조제3항, 같은 법 시행령 제11조제1호
 전자정부법 제7조제1항·제3항·제5항</t>
@@ -580,7 +580,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>[현행 규정] 민원처리법 제8조: 민원 신청은 문서(전자문서 포함)로 함. 제8조의2①: '민원인은 민원의 처리에 필요한 증명서류나 구비서류를 「전자정부법」 제2조제7호에 따른 전자문서나 같은 조 제8호에 따른 전자화문서로 제출할 수 있다. 다만, 행정기관이 전자문서나 전자화문서로 증명서류나 구비서류를 받을 수 있는 정보시스템을 구축하지 아니한 경우 등 대통령령으로 정하는 사유가 있는 경우에는 그러하지 아니하다.' 제22조①: 보완이 필요하면 상당한 기간을 정하여 지체 없이 보완 요구, ③: 보완 절차·방법은 대통령령. 시행령 제5조: 직접 방문이 필요 없는 민원은 정보통신망·우편 등으로 신청 가능. 제5조의2①: 전자 제출의 예외 = 1. 전자문서를 받을 수 있는 정보시스템을 구축하지 않은 경우, 2. 시스템 장애, 3. 판독 불가 수신, 4. 다른 법령의 별도 규정; ②: 그 경우 지체 없이 알리고 방문·우편·팩스 등 다른 방법을 안내. 제24조①: 보완 '요구'는 문서 또는 구술 등으로(민원인이 요청하면 문서), ②~④: 보완기간 연장·재요구·기간 계산 — 민원인이 보완서류를 제출하는 방법은 규정하지 않음. 제6조⑧: 전자민원창구 신청은 도달 후 8근무시간 이내 접수. 행정절차법 시행령 제11조1호: 보완 소요 기간(보완을 위해 신청서를 신청인에게 발송한 날과 보완되어 행정청에 도달한 날 포함)은 처리기간에 불산입. 법 제12조의2①: 행정기관의 장은 민원인이 방문하지 않고도 민원을 처리할 수 있도록 관계법령 개선·정보시스템 구축 등 필요한 조치를 하여야 함.
+          <t>[현행 규정] 민원처리법 제8조: 민원 신청은 문서(전자문서 포함)로 함. 제8조의2①(신설 2022.1.11, 법률 제18698호 — 사용자 확인): '민원인은 민원의 처리에 필요한 증명서류나 구비서류를 「전자정부법」 제2조제7호에 따른 전자문서나 같은 조 제8호에 따른 전자화문서로 제출할 수 있다. 다만, 행정기관이 전자문서나 전자화문서로 증명서류나 구비서류를 받을 수 있는 정보시스템을 구축하지 아니한 경우 등 대통령령으로 정하는 사유가 있는 경우에는 그러하지 아니하다.' 제22조①: 보완이 필요하면 상당한 기간을 정하여 지체 없이 보완 요구, ③: 보완 절차·방법은 대통령령. 시행령 제5조: 직접 방문이 필요 없는 민원은 정보통신망·우편 등으로 신청 가능. 제5조의2①: 전자 제출의 예외 = 1. 전자문서를 받을 수 있는 정보시스템을 구축하지 않은 경우, 2. 시스템 장애, 3. 판독 불가 수신, 4. 다른 법령의 별도 규정; ②: 그 경우 지체 없이 알리고 방문·우편·팩스 등 다른 방법을 안내. 제24조①: 보완 '요구'는 문서 또는 구술 등으로(민원인이 요청하면 문서), ②~④: 보완기간 연장·재요구·기간 계산 — 민원인이 보완서류를 제출하는 방법은 규정하지 않음. 제6조⑧: 전자민원창구 신청은 도달 후 8근무시간 이내 접수. 행정절차법 시행령 제11조1호: 보완 소요 기간(보완을 위해 신청서를 신청인에게 발송한 날과 보완되어 행정청에 도달한 날 포함)은 처리기간에 불산입. 법 제12조의2①: 행정기관의 장은 민원인이 방문하지 않고도 민원을 처리할 수 있도록 관계법령 개선·정보시스템 구축 등 필요한 조치를 하여야 함.
 [문제점] ① 제8조의2①이 구비서류의 전자 제출을 민원인의 권리로 규정했으나 보완 단계에 적용된다는 명시가 없고, 시행령 제24조는 행정청의 보완 '요구' 방법만 규정하여 '신청은 전자로, 보완은 방문으로'라는 운용을 막는 조문이 없음(인터뷰: 이메일 보완 '절대 안 된다', '재량'). ② 제8조의2① 단서와 시행령 제5조의2①1호의 예외가 '행정기관이 정보시스템을 구축하지 아니한 경우'로 되어 있어, 전자민원창구에 보완서류 제출 기능을 두지 않은 기관은 자신의 미구축을 이유로 전자 제출을 거부할 수 있고 구축 기한이나 최소 기능에 관한 의무가 없어 예외가 사실상 재량처럼 작동함. ③ 보완기간은 처리기간에 산입되지 않으므로(행정절차법 시행령 제11조1호) 방문 보완 요구는 법정 처리기간 통계에 드러나지 않은 채 신고인의 시간·교통비만 늘림(인터뷰이 추정: 보완 요구 중 방문 요구 30~40%).
 [논거] 민원처리법 제12조의2①(비방문 처리를 위한 법령 개선·시스템 구축 의무)과 제8조의2①(전자 제출 권리)의 취지상 보완도 신청과 같은 방법으로 할 수 있어야 하고, 보완은 신청의 연장이므로 신청보다 엄격한 방식을 요구할 합리적 이유가 없음(비례원칙). 전자정부법 제7조①·③: 관계 법령이 종이문서를 정하고 있어도 전자문서·전자화문서로 신청·첨부 가능. 행정절차법 시행령 제11조1호가 보완서류의 '발송·도달'을 전제하는 것과 체계상 부합. 체계 정합성: 신청(제8조·시행령 제5조), 접수(시행령 제6조⑧), 결과 통지(법 제27조②)는 전자 처리가 명문화되어 있고 보완 단계만 공백.
 [개정 방향] ① (시행령 제24조) 신설 항: '민원인은 제1항에 따라 요구받은 보완을 법 제8조의2제1항에 따른 전자문서·전자화문서 또는 제5조에 따른 방법으로 할 수 있다. 이 경우 제5조의2를 준용한다.' ② (시행령 제24조①) 보완을 요구할 때 보완의 방법과 보완기간이 처리기간에 산입되지 않는다는 사실을 함께 알리도록 명시. ③ (시행령 제5조의2①1호) '정보시스템을 구축하지 않은 경우'에 '통합전자민원창구를 통하여 받을 수 있는 경우는 제외한다'를 추가하여, 정부24 등 통합창구로 받을 수 있으면 미구축 예외를 원용할 수 없도록 함. ④ 시스템: 정부24 접수 민원의 보완서류 업로드 기능 — 운영 사항. ①~③은 대통령령 개정으로 가능(법률 개정 불요).
@@ -628,11 +628,11 @@
 [문제점] ① 민간이 주최하는 축제·행사는 열거 항목에 없고 (9)의 '별도 지정'에만 의존하므로, 지정 여부가 전적으로 지자체 재량이 되어 같은 행사 유형에 대해 A군은 허용·B군은 불허하는 편차가 법령 구조 자체에서 발생함(인터뷰: 지자체 주최 행사만 허용 vs 장소 위생만 심사). ② (9)의 지정에 기준·절차·공표 의무가 없어 신고인이 사전에 가능 여부를 알 수 없고, 불허 시에도 '그 지역은 안 된다' 외에 이유가 제시되지 않음(행정절차법 제23조①). ③ 정부24에 온라인 신고 가능으로 표시되나 별표 14의 장소 요건과 지자체별 지정 현황은 안내되지 않아 행정절차법 제40조①(신고 요건 게시 의무)과 괴리. ④ 수범자인 행정사조차 '상위법에 규정이 없다'고 인식할 정도로 특례 규정이 별표 깊숙이 있어 접근성이 낮고, 제42조③이 '영업신고증 제출'로만 규정되어 법 제37조⑫의 3일 내 수리 통지가 적용되는 신고인지 문언상 불명확.
 [논거] 행정규제기본법 제4조①: 규제 내용은 '알기 쉬운 용어로 구체적이고 명확하게' 규정. 행정절차법 제40조①: 신고 요건·접수기관 등 게시 의무. 평등원칙·예측가능성: 조례 위임도 없이 지자체 지정 유무에 따라 동일 법령의 허용 범위가 달라지는 것은 법령이 스스로 편차를 허용한 구조. 동일 지역에서 지자체 행사와 민간 행사의 위생 위험이 주최자에 따라 달라지지 않으므로 '주최·주관·후원' 요건은 수단의 적합성이 약함.
 [개정 방향] ① (시행규칙 별표 14 제8호가목5)가) 및 제2호사목) (7)에 '민간이 주최하는 지역행사로서 특별자치시장ㆍ특별자치도지사ㆍ시장ㆍ군수ㆍ구청장이 위생ㆍ안전 관리계획을 확인한 행사'를 추가하거나, (9)에 '지정 기준과 지정 장소를 미리 정하여 공표하여야 한다'는 단서를 신설. ② (시행규칙 제42조③) 한시적 영업신고에 법 제37조⑫·⑬이 적용됨을 명시하고 불허 시 사유 통지를 민원처리법 제27조③에 따라 운용하도록 규정. ③ (시스템·운영) 정부24 한시적 영업신고 안내에 별표 14 장소 요건과 지자체별 지정 장소 링크 표시 — 운영 사항.
-[유의] 식약처 소관. 인터뷰이 발언('상위법에도 규정이 없다', '조례에 의한 것도 아니다')은 법령 확인 결과와 다름 — 규정은 있으나 민간 행사 허용 여부가 지자체 지정에 위임된 구조이며, 그 차이는 검토메모 24에 기록. 민간 행사 포함은 특례 범위 확대(규제 완화)로 신고제도 범위 내이나 위생사고 위험에 대한 식약처 입장 확인 필요. 지자체 안내문(진안군 등) 등 2차 자료는 접속 차단으로 원문 미확인. 특정 지자체(허용·불허 사례의 지역명)가 발언에서 특정되지 않아 지자체 간 편차 주장은 입법사실로서 보강이 필요함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="227" customHeight="1">
+[유의] 식약처 소관. 인터뷰이 발언('상위법에도 규정이 없다', '조례에 의한 것도 아니다')은 법령 확인 결과와 다름 — 규정은 있으나 민간 행사 허용 여부가 지자체 지정에 위임된 구조이며, 그 차이는 검토메모 25에 기록. 민간 행사 포함은 특례 범위 확대(규제 완화)로 신고제도 범위 내이나 위생사고 위험에 대한 식약처 입장 확인 필요. 지자체 안내문(진안군 등) 등 2차 자료는 접속 차단으로 원문 미확인. 특정 지자체(허용·불허 사례의 지역명)가 발언에서 특정되지 않아 지자체 간 편차 주장은 입법사실로서 보강이 필요함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="279" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -648,40 +648,40 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>청연 행정사 사무소·이종서(행정사)(기업 인증(벤처·이노비즈·기업부설연구소), 폐기물 인허가, 평생교육시설, 동물 관련 영업, 노인복지시설)</t>
+          <t>행정사 사무소 법연·박정모(행정사)(외국인 출입국 업무, 소상공인·중소기업 신고·인허가)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>평생교육법 제33조제2항, 제35조제2항, 제36조제3항, 제37조제3항, 제38조제3항, 제38조의2
-평생교육법 시행령 제48조, 제49조제1항·제3항, 제64조제2항, 제65조제2항(원문 미대조), 제66조제2항, 제67조제2항
-평생교육법 시행규칙 제17조제2항·제3항, 별지 제14호서식(처리기간 10일)
-행정기본법 제34조, 행정절차법 제40조제2항~제4항</t>
+          <t>식품위생법 제37조제4항·제12항·제13항
+식품위생법 시행규칙 제42조제8항·제11항, 제43조제1항(2021.12.30 신설, 2026.9.1 개정)·제2항, 별표 17 제7호(식품접객업자 준수사항), 별지 제41호서식(유의사항 3, 처리절차)
+민원 처리에 관한 법률 제27조제1항·제2항·제4항, 같은 법 시행령 제25조제4항·제29조제1항
+전자정부법 제7조제2항</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[인터뷰 내용] 민간 자격증·취미 교육(공방 등)을 위한 평생교육시설 설치는 법률상 '설치 신고'이지만 운영규칙·커리큘럼·소방·건축 요건 등 서류가 상당하고 반려가 많아 '등록 이상'으로 운영됨. 원격 시설은 완화되어 있으나 오프라인 시설은 요건이 많음. 바우처(평생교육이용권) 수요로 신고 수요가 늘고 있음.
-[발언] 이종서: "그렇죠 많이 하시죠. 왜냐면은 자격증 같은 것도 이제 민간으로 하려고 하시는 분들, 이것도 이제 신고 말은 설치 신고거든요. 설치 신고인데 그게 이제 서류나 뭐 이런 것들이 상당해요. 그 내용부터 해가지고 그리고 이것도 이제 반려하는 경우가 되게 많습니다. 이제 꾸려야 되는 커리큘럼이라든가 운영이라든가 그리고 또 오프라인 교육장 시설 소방시설부터 해가지고 건축법 또 맞춰야 되죠. 그런 것들을 해가지고 근데 말은 신고인데 거의 등록 이상인 것 같아요." / 이종서: "그렇죠. 이제 원격 평생교육 시설은 조금 완화가 돼 있고 지금 오프라인 경우에는 설치 요건이 조금 더 많죠." / 이종서: "그냥 민간인들도 많이 하세요. 최근에 했던 게 소잉이라고 해가지고 말 그대로 공방인 거죠. 평생교육 시설이 일반인이 할 수 있는 분야가 있고 언론기관, 회사의 부서 안, 대학 부설 기존엔 그렇게 많이 했었죠." / 이종서: "그렇죠. 폐기물 인허가 이런 것들 그리고 이제 평생교육 시설 같은 경우에도 그런 것들로 사업 계획서를 꾸려야 돼요."</t>
+          <t>[인터뷰 내용] 종로구 옥외영업 신고에서 수리기간이 지나도 답변이 없어 확인해 보니 담당 공무원이 결재를 올리지 않아 절차가 진행되지 않은 상태였음. 간단한 신고는 담당자 선에서 처리되어 담당자 역량 차이가 크고, 법정 기한을 넘기면 그 이유를 설명받고 싶다고 함. 수리 간주 제도에 대해서는, 간주되더라도 결국 가서 증명서(신고증)를 다시 발급받아야 하면 실효성이 없다고 평가.
+[발언] 박정모: "그러면은 담당자의 역량 차이가 정말 커요. 한 번은 이제 종로구에서 옥외영업 신고를 하는데 수리기간이 지나고 답변이 안 오는 거예요. 나중에 물어봤더니 절차가 진행이 안 된 것 같대요. 왜 절차가 진행이 안 됐냐 그랬더니 뭐 담당 공무원이 안 올린 거죠. 그래서 복잡한 거 말고 간단한 건 거의 담당자 선에서 이제 문제가 있어요." / (면담자 오세영) "법정 기한이 있잖아요? 그거를 넘겨서 처리를 보통은 안 하지 않나요?" 박정모: "보통은 안 해요. 그래서 이게 왜 넘어갔는지를 좀 설명을 듣고 싶은데." / 박정모: "그다음에 아까도 계속 말씀드린 수리 간주는 아무런 후속 절차 없이 일을 할 수 있으면 모르겠지만 내가 가서 증명서를 다시 발급받아야 되고 이런 문제라고 한다면은 기간의 차이는 조금 있을 수도 있겠지만은 크게 실효성은 없지 않나는 생각을 합니다." / 박정모: "그러다 보니까는 수리 간주나 이런 것도 자기 완결이 된다고 하더라도 어차피 가서 받는 서류가 있으니까요. 이런게 자동으로 출력이 되면 상관이 없는데, 그렇게 해주지는 않을 거잖아요. 그쪽도 결제 라인이라는 게 있는 거니까."</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[현행 규정] 평생교육법 제33조②: 원격교육 형태 평생교육시설은 '대통령령으로 정하는 바에 따라 교육감에게 신고하여야 한다'. 제35조②(사업장 부설)·제36조③(시민사회단체 부설)·제37조③(언론기관 부설)·제38조③(지식·인력개발 관련)도 같은 문언. 법률에는 수리 여부 통지 기한, 수리 간주, 수리 거부 사유 규정이 없음. 시행령 제49조③: '교육감은 제1항에 따른 신고가 있는 경우에는 이를 검토하여 요건에 해당하면 교육부령으로 정하는 신고증을 내주어야 한다'(제64조②·제66조②·제67조②에서 준용). 시행규칙 제17조②: 첨부서류 8종(위치도·시설배치도·시설설비 현황표·평생교육사 자격증·정관·회의록·재산목록 및 증명서류·임대차계약서 사본). 별지 제14호서식(개정 2024.6.18): 처리기간 10일, 처리절차 '접수 및 검토→결재→신고증 작성→대장 기재→교부'.
-[문제점] ① 법률은 '신고'만 규정하고 수리를 명시하지 않았는데 시행령이 '검토하여 요건에 해당하면 신고증 교부'라는 심사형 절차를 두어, 수리가 필요한 신고는 법률에 명시하도록 한 행정기본법 제34조와의 정합성 문제가 있음. 수리 필요 신고라면 법률에 근거가, 자기완결적 신고라면 행정절차법 제40조②에 따라 형식 요건 구비 시 도달로 의무가 이행되어야 하는데 어느 쪽인지 법문상 불명확하여 교육청이 실질 심사·반려를 반복(인터뷰: '반려하는 경우가 되게 많습니다', '거의 등록 이상'). ② 처리기간 10일은 서식에만 있고 법령에 수리 여부 통지 기한·간주 규정이 없어, 2018~2019년 신고제도 정비에서 채택된 표준(식품위생법 제37조⑫⑬, 폐기물관리법 제46조③④ 등)에서 누락된 형태. ③ '요건'의 내용이 시행령 제49조①·②의 신고서·운영규칙 기재사항 수준에 머물러 어떤 사유로 반려되는지 예측하기 어렵고, 소방·건축 요건은 시설기준 조문이 아니라 심사 과정에서 요구됨.
-[논거] 행정기본법 제34조(수리 필요 신고의 법률 명시). 행정절차법 제40조②~④(형식 요건 미비 시 보완 요구, 미보완 시 이유를 밝혀 반려). 법률유보: 신고의 효력 발생 요건(수리 여부)은 영업의 자유에 직접 영향을 주는 사항이므로 법률 사항. 같은 법 안의 정합성: 제31조(학교형태 등록), 제32조·제33조③(인가)과 구분되는 '신고'의 효과가 하위법령에서 등록·인가와 유사하게 운용됨.
-[개정 방향] ① (법률) 제33조②·제35조②·제36조③·제37조③·제38조③에 '교육감은 신고를 받은 날부터 10일 이내에 신고수리 여부를 신고인에게 통지하여야 한다. 그 기간 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 신고를 수리한 것으로 본다'는 취지의 표준 조항 신설. ② (시행령 제49조③) '검토하여 요건에 해당하면'을 법률의 수리 규정과 연결하고, 검토 대상 요건을 시행령·규칙의 설치기준 조문으로 특정. ③ (최소 정비안, 하위법령만) 시행령 제49조에 처리기간(10일)과 보완 요구·반려 절차(행정절차법 제40조③·④ 준용)를 명시하고, 시행규칙 제17조② 첨부서류 중 공동이용으로 확인 가능한 서류를 제3항으로 이관.
-[유의] 교육부 소관. 인터뷰이가 다룬 사례의 시설 유형(원격/오프라인, 어느 조문의 시설인지)이 특정되지 않아 조문 확정에 한계가 있음 — 개인이 설치하는 오프라인 시설은 제38조(지식·인력개발, 법인·자본금 3억 요건)에 해당하지 않을 수 있고 학원법 대상일 가능성도 있음. 2026.6.2 공포(2026.12.3 시행) 평생교육법 개정 내용은 원문 미대조. 시행령 제65조(시민사회단체 부설)는 목차만 확인.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="227" customHeight="1">
+          <t>[현행 규정] 식품위생법 제37조⑫·⑬: 변경신고를 받은 날부터 3일 이내 수리 여부 미통지 시 기간이 끝난 날의 다음 날 수리 간주. 시행규칙 제42조⑧: (신규) 영업신고를 받은 신고관청은 지체 없이 영업신고증 발급, ⑪: 신고증 분실·훼손 시 재발급 신청. 제43조(변경신고): ① 변경신고서와 첨부서류를 변경한 날부터 7일 이내 제출, ② 공동이용 확인. 제43조①은 2021.12.30 개정(총리령 제1774호) 당시 '영업신고증 및 다음 각 호의 구분에 따른 서류를 첨부'로 규정되었으나 2026.9.1 개정으로 '영업신고증 및' 문구가 삭제됨(사용자 제공 신구조문대비표와 현행 조문 대조) — 변경신고 수리 후 신고증에 변경사항을 기재하거나 재발급하는 조항은 어느 시기에도 없음. 별표 17(제57조 관련, 개정 2026.9.1) 제7호 식품접객업자 준수사항: 조리사면허증 보관, 가격표·간판 상호 표시, 신고관청 요청 사항 게시 의무만 있고 영업신고증의 비치·게시 의무는 없음. 별지 제41호서식: 처리기간 '즉시', 처리절차에 '신고증 발급' 표기, 유의사항 3 '영업신고증을 잃어버린 경우에는 변경사유란에 그 사유를 적고 영업신고증은 첨부하지 않아도 됩니다'(신고증 첨부를 전제). 민원처리법 제27조①: 처리 완료 시 문서 통지, ②: 전자민원 신청 시 전자문서 통지로 갈음 가능, ④: 신고필증 등 직접 교부 시 본인·위임 확인. 전자정부법 제7조②: 종이문서 통지 규정이 있어도 전자문서로 통지 가능.
+[문제점] ① 종로구 사례는 법 제37조⑬에 따라 3일 경과 다음 날 이미 수리 간주된 상태였는데도 신고인은 이를 알 수 없었고 신고증도 받지 못했음 — 간주의 법적 효과가 신고인에게 전달되는 수단(통지·신고증)이 변경신고에 관하여는 법령에 특정되어 있지 않음. ② 제43조에는 변경신고 수리(간주 포함) 후 신고증 기재·재발급 조항이 없고 서식에만 '신고증 발급'이 표기되어 조문과 서식이 불일치하며, 신고증 첨부 의무도 조문 없이 서식 유의사항에만 전제됨. ③ 영업신고증을 '어차피 가서 받는 서류'로 보는 인터뷰이의 전제는 별표 17 확인 결과 법령상 비치·게시 의무가 아니라 실무 관행임. 그러나 신고증은 영업신고 사실을 증명하는 유일한 법정 문서(시행규칙 제42조⑧ 발급 의무)이고 2026.9.1 개정 전까지는 변경신고 자체에 신고증 첨부가 요구되었으므로, 간주 후에도 변경사항이 기재된 신고증을 받으려면 신고인이 다시 방문·요청해야 하는 구조에서는 수리 간주가 지연 통제 수단으로 기능하지 못함.
+[논거] 상·하위법령 정합성(법률의 수리 간주 ↔ 시행규칙의 신고증 절차 공백 ↔ 서식의 처리절차 표기). 민원처리법 제27조①·시행령 제29조①: 처리 완료 시 지체 없이 교부 또는 정보통신망·우편 통지 의무 — 간주로 처리가 완료된 경우에도 적용된다고 보아야 하나 명문 규정 없음. 전자정부법 제7조②·민원처리법 제27조②: 전자문서 신고증 교부가 가능하므로 '자동 출력'은 법령상 장애가 없고 시행규칙에 근거만 두면 됨.
+[개정 방향] ① (시행규칙 제43조) 신설 항: '신고관청은 변경신고를 수리(법 제37조제13항에 따라 수리한 것으로 보는 경우를 포함한다)한 때에는 지체 없이 영업신고증에 변경사항을 적어 재발급(전자문서를 포함한다)하여야 한다.' 및 변경신고 시 신고증 첨부 또는 분실 시 사유 기재 규정을 조문으로 이관. ② (법률 또는 법제처 표준문안) 수리 간주 조항에 '간주된 경우 행정청은 신고인의 요청 없이 신고증을 교부하여야 한다'는 후속 절차를 범정부 표준으로 추가하는 방안 검토(식품위생법 제37조⑬에 우선 반영). ③ 운영: 담당자 미결재는 민원처리법 시행령 제21조②(담당자 부재 등을 사유로 한 연장 금지, 2026.5.6 신설)와 제22조 처리상황 확인·점검 사항.
+[유의] 식약처 소관(①), 법제처·행안부 협의(②). 별표 17에 영업신고증 비치 의무가 없다는 점은 인터뷰이 전제와 달라 검토메모 25에 기록했고, 그에 따라 문제점 ③의 논거를 '비치 의무'가 아닌 '간주 효과의 전달 수단 부재'로 한정함. 담당자가 결재를 올리지 않은 것 자체는 운영 문제이며 본표에 올린 것은 간주 후속 절차의 법령 공백에 한정함. 인터뷰이 사례는 2026년 종로구 1건이고 인터뷰이 본인 의견('수리 폐지는 안 된다', '간주는 실효성 없다')은 정책 선호로서 기록만 함. [교차확인] 연번 1(정은지 인터뷰)와 동일 쟁점. 검토메모 22(이종서 인터뷰, 사용자 판단으로 본표 제외) 참조.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="253" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026.8.26.</t>
+          <t>2026.8.28.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -691,53 +691,10 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>행정사 사무소 법연·박정모(행정사)(외국인 출입국 업무, 소상공인·중소기업 신고·인허가)</t>
+          <t>으뜸퍼스트 행정사사무소·이범원(행정사)(출입국, 건설업 등록, 식품·축산물 HACCP 인허가, 공장등록)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>식품위생법 제37조제4항·제12항·제13항
-식품위생법 시행규칙 제42조제8항·제11항, 제43조제1항·제2항, 별지 제41호서식(유의사항 3, 처리절차)
-민원 처리에 관한 법률 제27조제1항·제2항·제4항, 같은 법 시행령 제25조제4항·제29조제1항
-전자정부법 제7조제2항</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 종로구 옥외영업 신고에서 수리기간이 지나도 답변이 없어 확인해 보니 담당 공무원이 결재를 올리지 않아 절차가 진행되지 않은 상태였음. 간단한 신고는 담당자 선에서 처리되어 담당자 역량 차이가 크고, 법정 기한을 넘기면 그 이유를 설명받고 싶다고 함. 수리 간주 제도에 대해서는, 간주되더라도 결국 가서 증명서(신고증)를 다시 발급받아야 하면 실효성이 없다고 평가.
-[발언] 박정모: "그러면은 담당자의 역량 차이가 정말 커요. 한 번은 이제 종로구에서 옥외영업 신고를 하는데 수리기간이 지나고 답변이 안 오는 거예요. 나중에 물어봤더니 절차가 진행이 안 된 것 같대요. 왜 절차가 진행이 안 됐냐 그랬더니 뭐 담당 공무원이 안 올린 거죠. 그래서 복잡한 거 말고 간단한 건 거의 담당자 선에서 이제 문제가 있어요." / (면담자 오세영) "법정 기한이 있잖아요? 그거를 넘겨서 처리를 보통은 안 하지 않나요?" 박정모: "보통은 안 해요. 그래서 이게 왜 넘어갔는지를 좀 설명을 듣고 싶은데." / 박정모: "그다음에 아까도 계속 말씀드린 수리 간주는 아무런 후속 절차 없이 일을 할 수 있으면 모르겠지만 내가 가서 증명서를 다시 발급받아야 되고 이런 문제라고 한다면은 기간의 차이는 조금 있을 수도 있겠지만은 크게 실효성은 없지 않나는 생각을 합니다." / 박정모: "그러다 보니까는 수리 간주나 이런 것도 자기 완결이 된다고 하더라도 어차피 가서 받는 서류가 있으니까요. 이런게 자동으로 출력이 되면 상관이 없는데, 그렇게 해주지는 않을 거잖아요. 그쪽도 결제 라인이라는 게 있는 거니까."</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>[현행 규정] 식품위생법 제37조⑫·⑬: 변경신고를 받은 날부터 3일 이내 수리 여부 미통지 시 기간이 끝난 날의 다음 날 수리 간주. 시행규칙 제42조⑧: (신규) 영업신고를 받은 신고관청은 지체 없이 영업신고증 발급, ⑪: 신고증 분실·훼손 시 재발급 신청. 제43조(변경신고): ① 변경신고서와 첨부서류를 변경한 날부터 7일 이내 제출, ② 공동이용 확인 — 변경신고 수리 후 신고증에 변경사항을 기재하거나 재발급하는 조항 없음. 별지 제41호서식: 처리기간 '즉시', 처리절차에 '신고증 발급' 표기, 유의사항 3 '영업신고증을 잃어버린 경우에는 변경사유란에 그 사유를 적고 영업신고증은 첨부하지 않아도 됩니다'(신고증 첨부를 전제). 민원처리법 제27조①: 처리 완료 시 문서 통지, ②: 전자민원 신청 시 전자문서 통지로 갈음 가능, ④: 신고필증 등 직접 교부 시 본인·위임 확인. 전자정부법 제7조②: 종이문서 통지 규정이 있어도 전자문서로 통지 가능.
-[문제점] ① 종로구 사례는 법 제37조⑬에 따라 3일 경과 다음 날 이미 수리 간주된 상태였는데도 신고인은 이를 알 수 없었고 신고증도 받지 못했음 — 간주의 법적 효과가 신고인에게 전달되는 수단(통지·신고증)이 변경신고에 관하여는 법령에 특정되어 있지 않음. ② 제43조에는 변경신고 수리(간주 포함) 후 신고증 기재·재발급 조항이 없고 서식에만 '신고증 발급'이 표기되어 조문과 서식이 불일치하며, 신고증 첨부 의무도 조문 없이 서식 유의사항에만 전제됨. ③ 영업신고증은 영업장 비치·점검 대상이라는 실무 전제(인터뷰이: '어차피 가서 받는 서류')에서, 간주 후에도 신고인이 방문해 재발급을 요청해야 하면 수리 간주는 지연 통제 수단으로 기능하지 못함.
-[논거] 상·하위법령 정합성(법률의 수리 간주 ↔ 시행규칙의 신고증 절차 공백 ↔ 서식의 처리절차 표기). 민원처리법 제27조①·시행령 제29조①: 처리 완료 시 지체 없이 교부 또는 정보통신망·우편 통지 의무 — 간주로 처리가 완료된 경우에도 적용된다고 보아야 하나 명문 규정 없음. 전자정부법 제7조②·민원처리법 제27조②: 전자문서 신고증 교부가 가능하므로 '자동 출력'은 법령상 장애가 없고 시행규칙에 근거만 두면 됨.
-[개정 방향] ① (시행규칙 제43조) 신설 항: '신고관청은 변경신고를 수리(법 제37조제13항에 따라 수리한 것으로 보는 경우를 포함한다)한 때에는 지체 없이 영업신고증에 변경사항을 적어 재발급(전자문서를 포함한다)하여야 한다.' 및 변경신고 시 신고증 첨부 또는 분실 시 사유 기재 규정을 조문으로 이관. ② (법률 또는 법제처 표준문안) 수리 간주 조항에 '간주된 경우 행정청은 신고인의 요청 없이 신고증을 교부하여야 한다'는 후속 절차를 범정부 표준으로 추가하는 방안 검토(식품위생법 제37조⑬에 우선 반영). ③ 운영: 담당자 미결재는 민원처리법 시행령 제21조②(담당자 부재 등을 사유로 한 연장 금지, 2026.5.6 신설)와 제22조 처리상황 확인·점검 사항.
-[유의] 식약처 소관(①), 법제처·행안부 협의(②). 담당자가 결재를 올리지 않은 것 자체는 운영 문제이며 본표에 올린 것은 간주 후속 절차의 법령 공백에 한정함. 인터뷰이 사례는 2026년 종로구 1건이고 인터뷰이 본인 의견('수리 폐지는 안 된다', '간주는 실효성 없다')은 정책 선호로서 기록만 함. [교차확인] 연번 1(정은지 인터뷰)와 동일 쟁점. 검토메모 22(이종서 인터뷰, 사용자 판단으로 본표 제외) 참조.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="253" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026.8.28.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>행정사</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>으뜸퍼스트 행정사사무소·이범원(행정사)(출입국, 건설업 등록, 식품·축산물 HACCP 인허가, 공장등록)</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>축산물 위생관리법 제9조제3항·제4항(신설 2020.4.7), 제22조제1항, 제25조
 축산물 위생관리법 시행규칙 제7조제3항(개정 2024.1.12), 제7조의3제1항·제2항·제6항, 제37조제1항, 별지 제28호서식(개정 2024.1.12)
@@ -747,19 +704,19 @@
 (비교) 식품위생법 제48조제2항·제3항, 같은 법 시행규칙 제62조</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>[인터뷰 내용] 축산물가공업(서대문구 사례)은 영업허가를 받은 뒤 품목제조보고를 하고 한국식품안전관리인증원에 HACCP 인증을 신청하는 순서인데, 구청 위생과가 품목제조보고를 받기 위해 HACCP 인증을 먼저 받아오라고 요구함. 인증에 수천만 원이 드는 데다 인증 심사는 운용 실적을 보므로 '인증 후 품목보고' 요구는 모순이며, 결국 사전 인증심사 관련 서류를 먼저 내는 방식으로 해결. 순환보직으로 담당자가 제도를 숙지하지 못하는 것이 원인으로 보임. 축산물은 2024년부터 HACCP 전면 의무.
 [발언] 이범원: "등록 이제 잘 아시겠지만 신고 등록 허가가 있는데 축산물 가공업은 좀 이제 아무래도 위생 관련돼서 허가 쪽으로 돼 있어요." / 이범원: "일반 식품은 등록제인데 거기에 이제 주 서대문에서 했었는데 이제 축산물 가공업을 하려고 그러면 해썹 인증이 기본이에요." / 이범원: "그런데 시작은 허가를 먼저 맡아야죠. 그래서 등록 관청에다가 허가를 등록을 하고 그다음에 이제 그걸 득한 다음에 한국식품인증관리원에 인증을 신청을 합니다." / 이범원: "허가를 받고 그다음에 품목 제조 보고라는 게 있어요." / 이범원: "이제 예를 들어서 햄을 만든다고 그러면 햄을 할 때 그러면 이 햄을 햄류를 또 품목 지수 보고를 신고를 해가지고 내주는 데가 구청이에요." / 이범원: "위생과 그럼 거기서 또 뭐라고 그러냐면 그거 품목 제조 받기 위해서 해썹 인증을 먼저 받아오라 이런 얘기예요." / 이범원: "그런 얘기를 해요. 엉뚱한 얘기죠. 그러면 해썹 인증을 하기 위해서는 돈이 수천만 원이 들어가는데 그거를 먼저 해놓고 품목 제조 보고를 한다." / 이범원: "그래서 그런 부분에 이제 트러블이 좀 있었었고 그래서 이제 결국은 사전 인증 심사 증을 하나 먼저 내고 이런 식으로 하는 그런 거 했는데 그거는 좀 모순이 되는 부분이에요." / 이범원: "육가공이 2024년도부터 전체가 다 그랬죠. 유제품까지 다"</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>[현행 규정] 축산물 위생관리법 제9조③(신설 2020.4.7): 축산물가공업 영업자 중 총리령으로 정하는 영업자(시행규칙 제7조③: 식육가공업·유가공업·알가공업 영업자 — 2024.1.12 개정으로 매출·종업원 단계 구분 삭제)와 식용란선별포장업·식육포장처리업 영업자는 안전관리인증기준을 '지켜야 한다'. ④: 식약처장은 지켜야 하는 영업자의 준수 여부를 심사하여 인증'할 수 있다'. 시행규칙 제7조의3①·②: 인증 신청은 인증원장에게 운용 계획서 첨부, 요건은 위생관리프로그램 운용·교육 수료; ⑥: 서류검토·현장조사로 기준 준수가 인정되면 인증서 발급. 법 제25조·시행규칙 제37조①·별지 제28호서식: 품목제조보고는 '제품생산 개시 전이나 제품생산 개시 후 7일 이내'에 제조방법설명서·소비기한 설정사유서 등 3종을 첨부하여 허가관청에 제출 — HACCP 인증서는 첨부서류가 아님. 고시 제4조②: 의무적용 시기는 '각 법에서 정한 바에 따르되' 매출·종업원 기준, ③: 신규영업은 3개월 매출로 산정 가능·시설 개보수 시 1년 유예, ⑤: 시행규칙 제7조③1호가목(2024.1.12 삭제) 참조. 전면 의무화 이후 신규 축산물가공업자가 언제까지 인증을 받아야 하는지, 인증 전 생산·판매가 가능한지 정하는 조문은 법·령·규칙·고시 어디에도 없음.
 [문제점] ① 품목제조보고 첨부서류에 없는 HACCP 인증서를 허가관청(구청 위생과)이 선행 요구한 것은 민원처리법 제10조①(관계법령 외 서류 요구 금지) 위반이고, 인증 심사가 실제 운용 상태(현장조사)를 전제하므로 '인증 후 품목보고'는 절차 순서가 뒤바뀐 요구임. ② 근본 원인은 법 제9조③의 '지켜야 한다'와 ④의 '인증할 수 있다' 사이에, 의무적용 영업자가 ⓐ 인증 전에 영업·생산을 개시할 수 있는지, ⓑ 언제까지 인증을 신청·취득해야 하는지가 규정되지 않은 공백이며, 지자체가 이를 '인증 완료 후 생산'으로 보수적으로 해석하면 품목제조보고 단계에서 인증을 요구하게 됨. ③ 2024.1.12 전면 의무화 이후에도 고시 제4조⑤가 삭제된 시행규칙 조문을 참조하는 등 구법 체계의 문언이 남아 신규 영업자에게 적용되는 유예·기한을 읽어낼 수 없음.
 [논거] 규제 법정주의(행정규제기본법 제4조): 인증 취득 시한과 인증 전 영업 가능 여부는 영업자의 의무 범위를 정하는 사항이므로 법령에 명확히 규정되어야 함. 민원처리법 제10조①. 체계 정합성: 식품위생법 제48조②·③도 같은 '준수 의무 + 인증 가능' 구조이고 시행규칙 제62조①13호(매출 100억 기준)가 적용 시기를 정하므로, 축산물에도 적용 시기·기한 조문이 대응되어야 함. 신뢰보호: 영업허가(제22조)와 품목제조보고를 적법하게 마친 영업자가 인증 전 생산을 위법으로 취급받을 위험.
 [개정 방향] ① (법률 제9조 또는 시행규칙 제7조) 의무적용 영업자는 '영업허가를 받은 날(또는 해당 품목의 제조 개시일)부터 ○개월 이내에 제4항에 따른 인증을 신청하여야 하며, 인증 심사가 진행되는 기간 중에는 안전관리인증기준을 준수하여 생산·판매할 수 있다'는 취지의 신청 기한·과도기 규정 신설. ② (시행규칙 제37조①·별지 제28호서식) 첨부서류가 한정적 열거임과 인증서 제출 요구 불가를 서식 안내에 명시 — 운영 보조. ③ (고시 제4조⑤) 삭제된 시행규칙 조문을 참조하는 문언 정비.
-[유의] 식약처 소관. 인증 신청 기한 신설은 이미 적용 중인 의무의 이행 시기를 명확화하는 것이지만 기한 설정 자체가 영업자 부담으로 해석될 수 있어 규제영향 검토가 필요 → 사용자 판단 필요 항목(2차 보고 시점까지 답변 없어 본표 유지). 법률 용어는 '품목제조보고'(보고)이고 인터뷰이는 '신고'로 표현함(검토메모 24). 사례는 서대문구 1건. 식품위생법 제48조 체계와의 세부 비교는 시행규칙 제62조만 확인하고 고시의 식품 부분은 미대조.</t>
+[유의] 식약처 소관. 인증 신청 기한 신설은 이미 적용 중인 의무의 이행 시기를 명확화하는 것이지만 기한 설정 자체가 영업자 부담으로 해석될 수 있어 규제영향 검토가 필요 → 사용자 판단 필요 항목(2차 보고 시점까지 답변 없어 본표 유지). 법률 용어는 '품목제조보고'(보고)이고 인터뷰이는 '신고'로 표현함(검토메모 25). 사례는 서대문구 1건. 식품위생법 제48조 체계와의 세부 비교는 시행규칙 제62조만 확인하고 고시의 식품 부분은 미대조.</t>
         </is>
       </c>
     </row>
@@ -774,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1162,7 +1119,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>기준 2. 본표 연번 1·5 및 검토메모 22와 동일 제도[교차확인]. 증명 서류의 예시(소유자·관리단 동의서, 임대차계약서 특약 등)를 서식 안내에 두는 것은 부수 정비.</t>
+          <t>기준 2. 본표 연번 1·4 및 검토메모 22와 동일 제도[교차확인]. 증명 서류의 예시(소유자·관리단 동의서, 임대차계약서 특약 등)를 서식 안내에 두는 것은 부수 정비.</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1322,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>1차 본표(연번 4)에 수록했으나 2026.10.15 사용자 판단으로 본표 제외. 조문-서식 불일치(제43조 사후확인 근거 부재)는 본표 연번 1·5의 개정 방향 ①에 이미 포함됨. 통행로 폭 등 수치 기준을 별표에 명시하는 방향은 규제 신설 소지(기준 3)로 제외.</t>
+          <t>1차 본표(연번 4)에 수록했으나 2026.10.15 사용자 판단으로 본표 제외. 조문-서식 불일치(제43조 사후확인 근거 부재)는 본표 연번 1·4의 개정 방향 ①에 이미 포함됨. 통행로 폭 등 수치 기준을 별표에 명시하는 방향은 규제 신설 소지(기준 3)로 제외.</t>
         </is>
       </c>
     </row>
@@ -1394,53 +1351,79 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="162" customHeight="1">
+    <row r="25" ht="149" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>인터뷰이 발언과 법령·용어의 차이 기록(발언은 수정하지 않음)</t>
+          <t>[1차·2차 본표 → 제외] 평생교육시설 설치 신고 — '법률에 수리 통지·간주 규정이 없다'는 1차 판단은 조문 누락 오류(제38조의3 존재)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>(a) 이종서: 한시적 영업신고에 '상위법에도 규정이 없다' → 식품위생법 시행규칙 제42조③·별표 14 제8호가목5)에 규정 있음(민간 행사는 지자체장 '별도 지정'에 위임). (b) 이종서: 사업자등록증이 공동이용에서 빠져 있다 → 농지법 시행규칙 제7조④7호 등에 공동이용 서류로 명시. (c) 이범원: 전자 인감증명서는 관공서 제출 불가로 되어 있다 → 인감증명법 시행령 제13조②5호는 법원·금융기관 제출용만 제외. (d) 정은지: 농지취득자격증명 '면담 재량 조항' → 법·령·규칙·예규에서 미확인. (e) 박정모: 행정사 '영업신고' → 법률 용어 '업무신고'(행정사법 제10조, 검토메모 23). (f) 이범원: 품목제조보고를 '신고' → 법률 용어 '보고'(축산물 위생관리법 제25조). (g) 이종서: '신고는 7일 이내 수리, 허가는 15일' → 제도별 상이(식품위생법 신고 3일·서식 즉시, 폐기물 신고 20일, 행정사 업무신고 10일 등). (h) 이범원: 축산물가공업 '등록 관청에다가 허가를 등록' → 법률상 시·도지사 허가(제22조①). (i) 정은지: 보완서류 이메일 제출은 담당자 '재량' → 민원처리법 제8조의2①은 구비서류의 전자 제출을 민원인의 권리로 규정(예외는 시행령 제5조의2).</t>
+          <t>이종서(8.26): 민간 자격증·취미 교육(공방 등) 평생교육시설 설치는 '설치 신고'이지만 서류가 상당하고 반려가 많아 '등록 이상'으로 운영됨.
+이종서: "그렇죠 많이 하시죠. 왜냐면은 자격증 같은 것도 이제 민간으로 하려고 하시는 분들, 이것도 이제 신고 말은 설치 신고거든요. 설치 신고인데 그게 이제 서류나 뭐 이런 것들이 상당해요. 그 내용부터 해가지고 그리고 이것도 이제 반려하는 경우가 되게 많습니다. 이제 꾸려야 되는 커리큘럼이라든가 운영이라든가 그리고 또 오프라인 교육장 시설 소방시설부터 해가지고 건축법 또 맞춰야 되죠. 그런 것들을 해가지고 근데 말은 신고인데 거의 등록 이상인 것 같아요." / 이종서: "그렇죠. 이제 원격 평생교육 시설은 조금 완화가 돼 있고 지금 오프라인 경우에는 설치 요건이 조금 더 많죠."</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>각 조문은 참조 시트 참조.</t>
+          <t>평생교육법 제38조의3(신고 등의 처리절차, 2018.12.18 법률 제15964호로 신설, 부칙 제2조 적용례): ② '교육감은 제33조제2항 전단, 제35조제2항 전단, 제36조제3항 전단, 제37조제3항 전단 또는 제38조제3항 전단에 따른 신고를 받은 날부터 10일 이내에 신고수리 여부를 신고인에게 통지하여야 한다'(변경신고도 같음), ③ 기간 내 미통지 시 '그 기간이 끝난 날의 다음 날에 신고를 수리한 것으로 본다'. 시행령 제49조③(검토하여 요건에 해당하면 신고증 교부), 제65조②(제49조 준용 — 사용자 제공 3단비교표로 확인), 시행규칙 별지 제14호서식 처리기간 10일 = 법 제38조의3②와 일치. 2026.6.2 개정(법률 제21721호, 2026.12.3 시행)은 평생교육사 보수교육(제27조의2·제46조) 신설로 신고 조문 변경 없음(사용자 제공 시행령 개정령안 및 시행예정본 제33조·제38조 조회로 확인). 2026.5.19 개정(법률 제21662호, 2027.1.17 시행)은 사내대학원 관련(부칙 제2조)으로 제33조·제35조·제38조 변경 없음.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>검토메모 기록용.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="149" customHeight="1">
+          <t>1차·2차 본표에 '법률에 수리 여부 통지 기한·수리 간주 규정이 없어 행정기본법 제34조와 정합성 문제'로 수록했으나, 2026.10.15 부칙 검토 중 제38조의3을 발견하여 확인한 결과 수리 필요 신고임이 법률에 명시되어 있고 10일 통지·간주 표준 조항도 완비됨 → 1차·2차 서술은 작성자의 조문 누락 오류로 정정하고 본표에서 제외. 남는 쟁점(실체 요건 심사 기준의 불명확, 반려 빈발)은 시행령 제49조③ '요건'의 해석·운영 문제(기준 2) 또는 설치기준의 실체적 수준(기준 3)에 해당. 인터뷰이가 다룬 시설 유형이 특정되지 않은 한계는 그대로임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="214" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>인터뷰이 발언과 법령·용어의 차이 기록(발언은 수정하지 않음)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>(a) 이종서: 한시적 영업신고에 '상위법에도 규정이 없다' → 식품위생법 시행규칙 제42조③·별표 14 제8호가목5)에 규정 있음(민간 행사는 지자체장 '별도 지정'에 위임). (b) 이종서: 사업자등록증이 공동이용에서 빠져 있다 → 농지법 시행규칙 제7조④7호 등에 공동이용 서류로 명시. (c) 이범원: 전자 인감증명서는 관공서 제출 불가로 되어 있다 → 인감증명법 시행령 제13조②5호는 법원·금융기관 제출용만 제외. (d) 정은지: 농지취득자격증명 '면담 재량 조항' → 법·령·규칙·예규에서 미확인. (e) 박정모: 행정사 '영업신고' → 법률 용어 '업무신고'(행정사법 제10조, 검토메모 23). (f) 이범원: 품목제조보고를 '신고' → 법률 용어 '보고'(축산물 위생관리법 제25조). (g) 이종서: '신고는 7일 이내 수리, 허가는 15일' → 제도별 상이(식품위생법 신고 3일·서식 즉시, 폐기물 신고 20일, 행정사 업무신고 10일 등). (h) 이범원: 축산물가공업 '등록 관청에다가 허가를 등록' → 법률상 시·도지사 허가(제22조①). (i) 정은지: 보완서류 이메일 제출은 담당자 '재량' → 민원처리법 제8조의2①(2022.1.11 신설)은 구비서류의 전자 제출을 민원인의 권리로 규정(예외는 시행령 제5조의2). (j) 박정모: 수리 간주 후에도 '어차피 가서 받는 서류'가 있다 → 식품위생법 시행규칙 별표 17 제7호(식품접객업자 준수사항)에는 영업신고증 비치·게시 의무 없음(조리사면허증 보관 의무만 있음, 사용자 제공 별표 17 전문으로 확인). (k) [작성자 오류 정정] 1차·2차 본표의 '평생교육법에 수리 통지·간주 규정 없음' → 제38조의3(2018.12.18 신설)에 10일 통지·간주 규정 있음(검토메모 24).</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>각 조문은 참조 시트 참조.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>검토메모 기록용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="162" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>제외 쟁점 요약(4절 기준별)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>기준 1(운영·시스템 문제): 공동이용 미이행, 온라인 접수 기피·방문 유도, 농지취득자격증명 방문 요구, 여행업 보증보험 선요구, 결과 미통지·사유 미제시, 사전심사 미활용, 폐기물 신고를 허가로 오인, 서식 안내 부족, 처리결과 문서 방문 수령, 전자 인감증명서 불인정, 대리인 전자인증 부재, 담당자 부재·역량. 기준 2(해석·지침으로 해결): 폐기물 재활용 신고의 건축물 용도, 식품제조업 용도변경 부서 간 견해, 옥외영업 집합건물 동의서, 가이드라인 계층화 일반론, 대안 평가 의견. 기준 3(범위 외·규제 신설): 출입국(체류 허가·대행기관 전자민원·안내센터), 직접생산확인(공공조달), HACCP·동물보호법·가축사육 규제 수준, 영업정지 기간, 무자격 대행 제재·행정사법 계도, 아파트 입주자대표회의 포상 규정(공동주택관리법, 신고 아님), 공장등록 후 확인(문제 제기 아님). 사용자 판단으로 본표 제외(2026.10.15): 옥외영업 사전 현장확인(이종서, 검토메모 22), 행정사 업무신고 간주기간(박정모, 검토메모 23). 반대로 보완서류 전자 제출(정은지)은 1차 검토메모에서 본표 연번 2로 격상.</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>기준 1(운영·시스템 문제): 공동이용 미이행, 온라인 접수 기피·방문 유도, 농지취득자격증명 방문 요구, 여행업 보증보험 선요구, 결과 미통지·사유 미제시, 사전심사 미활용, 폐기물 신고를 허가로 오인, 서식 안내 부족, 처리결과 문서 방문 수령, 전자 인감증명서 불인정, 대리인 전자인증 부재, 담당자 부재·역량. 기준 2(해석·지침으로 해결): 폐기물 재활용 신고의 건축물 용도, 식품제조업 용도변경 부서 간 견해, 옥외영업 집합건물 동의서, 가이드라인 계층화 일반론, 대안 평가 의견. 기준 3(범위 외·규제 신설): 출입국(체류 허가·대행기관 전자민원·안내센터), 직접생산확인(공공조달), HACCP·동물보호법·가축사육 규제 수준, 영업정지 기간, 무자격 대행 제재·행정사법 계도, 아파트 입주자대표회의 포상 규정(공동주택관리법, 신고 아님), 공장등록 후 확인(문제 제기 아님). 사용자 판단으로 본표 제외(2026.10.15): 옥외영업 사전 현장확인(이종서, 검토메모 22), 행정사 업무신고 간주기간(박정모, 검토메모 23). 원문 대조로 본표 제외(2026.10.15): 평생교육시설 설치 신고(이종서, 검토메모 24 — 제38조의3 누락 오류 정정). 반대로 보완서류 전자 제출(정은지)은 1차 검토메모에서 본표 연번 2로 격상.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>본표 6건 외 쟁점은 모두 여기에 사유를 남김.</t>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>본표 5건 외 쟁점은 모두 여기에 사유를 남김.</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1514,7 +1497,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="84" customHeight="1">
+    <row r="4" ht="149" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>식품위생법 시행규칙(총리령)</t>
@@ -1527,7 +1510,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>제42조(①13호 외부 장소 사용권한 서류, ② 공동이용, ③ 한시적 영업·개정 2020.4.13, ⑧ 신고증 지체 없이 발급, ⑩ 발급 후 15일/1개월 내 시설 확인), 제43조(①·② 2개 항, jo 코드 재조회로 확인; 신고증 재발급·사후확인 조항 없음), 제62조 원문 확인. 별표 14(개정 2026.9.1) 전문 확인: 제8호가목5)가)(7)·(9), 제8호나목1)사), 제2호사목3)·6). 별지 제37호(영업신고서: 처리기간 즉시, 한시적 영업신고 수수료란, 담당공무원 확인사항 7종, 처리절차 '필요시 시설조사 15일 이내'), 별지 제41호(변경신고서: 처리기간 즉시, 유의사항 3 신고증 첨부 전제, 처리절차 '신고증 발급→필요시 시설조사') 서식 확인. 제42조·제43조 개정 연혁(옥외영업 허용 시점) 신구대조는 미대조.</t>
+          <t>제42조(①13호 외부 장소 사용권한 서류, ② 공동이용, ③ 한시적 영업·개정 2020.4.13, ⑧ 신고증 지체 없이 발급, ⑩ 발급 후 15일/1개월 내 시설 확인), 제43조(①·② 2개 항, jo 코드 재조회로 확인; 신고증 재발급·사후확인 조항 없음), 제62조 원문 확인. 별표 14(개정 2026.9.1) 전문 확인: 제8호가목5)가)(7)·(9), 제8호나목1)사), 제2호사목3)·6). 별지 제37호(영업신고서: 처리기간 즉시, 한시적 영업신고 수수료란, 담당공무원 확인사항 7종, 처리절차 '필요시 시설조사 15일 이내'), 별지 제41호(변경신고서: 처리기간 즉시, 유의사항 3 신고증 첨부 전제, 처리절차 '신고증 발급→필요시 시설조사') 서식 확인. [10.15 추가] 제42조·제43조 개정 연혁은 사용자 제공 신구조문대비표 2건으로 확인: 총리령 제1661호(2020.12.31 공포·2021.1.1 시행)에서 제42조①13호(외부 장소 사용권한 서류) 신설 및 제43조에 반영, 총리령 제1774호(2021.12.30)에서 제43조를 ①(변경 유형별 서류, '영업신고증 및 ...' 첨부)·②(공동이용)로 재편, 2026.9.1 개정으로 ①의 '영업신고증 및' 삭제(현행 조문과 대조). 별표 17(제57조 관련, 개정 2026.9.1) 전문은 사용자 제공 PDF로 확인 — 제7호 식품접객업자 준수사항에 영업신고증 비치·게시 의무 없음(조리사면허증 보관, 가격표·간판 표시, 신고관청 요청사항 게시만 규정). 별표 14 옥외영업장 안전시설 기준의 신설 시점은 미대조.</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1684,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
+    <row r="15" ht="71" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>평생교육법(법률)</t>
@@ -1714,7 +1697,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>제33조, 제35조, 제36조, 제38조, 제38조의2 원문 확인. 제37조는 서식 기재로 확인(조문 원문 미대조).</t>
+          <t>제33조, 제35조, 제36조, 제38조, 제38조의2 원문 확인(10.14). [10.15 추가] 제38조의3(신고 등의 처리절차, 2018.12.18 신설): ② 교육감은 신고·변경신고를 받은 날부터 10일 이내 수리 여부 통지, ③ 미통지 시 수리 간주 — 1차·2차 본표의 '법률에 수리 규정 없음' 서술은 조문 누락 오류로 정정(본표 제외). 시행예정본 조회: 2026.12.3 시행(법률 제21721호) 제33조·제38조 및 2027.1.17 시행(법률 제21662호) 제33조·제35조·제38조는 현행과 같은 문언, 제21721호는 제27조의2(평생교육사 보수교육) 신설. 제37조는 서식 기재로 확인.</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1714,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>목차 확인, 제48조·제49조·제64조·제66조·제67조 원문 확인(제49조③ '검토하여 요건에 해당하면 신고증'). 제65조는 목차만 확인.</t>
+          <t>목차 확인, 제48조·제49조·제64조·제66조·제67조 원문 확인(제49조③ '검토하여 요건에 해당하면 신고증'). 제65조②(제49조 준용)·제65조의2(제49조의2 준용)는 사용자 제공 3단비교표(대통령령 제36220호 기준)로 10.15 확인.</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1782,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>제8조, 제8조의2(구비서류의 전자적 제출 — 2026.10.15 추가 확인), 제9조, 제10조, 제12조의2, 제13조, 제17조, 제19조, 제22조, 제27조, 제30조 원문 확인.</t>
+          <t>제8조, 제8조의2(구비서류의 전자적 제출 — 2026.10.15 추가 확인; 신설 2022.1.11 법률 제18698호는 사용자 확인), 제9조, 제10조, 제12조의2, 제13조, 제17조, 제19조, 제22조, 제27조, 제30조 원문 확인.</t>
         </is>
       </c>
     </row>
@@ -2058,18 +2041,86 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="32" customHeight="1">
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
+          <t>[사용자 제공 10.15] 평생교육법 시행령 일부개정령안(법제처 심사 전, 교육부 평생학습정책과)</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>제출 2026년(일자 미기재), 시행 2026.12.3 예정</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>제안이유: 법률 제21721호(2026.6.2 공포)로 평생교육사 보수교육 조항 신설·불리한 처분 금지 → 과태료 부과기준(별표 9 제2호타목) 신설. 신고 조문과 무관함을 확인. input/법령원문_261015/pdf1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>[사용자 제공 10.15] 식품위생법 시행규칙 신구조문대비표 2건</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>총리령 제1651호→제1661호(2020.12.31 공포, 2021.1.1 시행); 제1715호→제1774호(2021.12.30)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>제42조①13호 신설, 제43조 재편 내용 확인(위 식품위생법 시행규칙 행 참조). input/법령원문_261015/pdf3, pdf2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>[사용자 제공 10.15] 평생교육법 시행령 3단비교표(제36조·제65조·제65조의2)</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>법률 제21080호·대통령령 제36220호·교육부령 제372호 기준</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>제65조② 제49조 준용, 제65조의2 제49조의2 준용 확인. input/법령원문_261015/pdf4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>[사용자 제공 10.15] 식품위생법 시행규칙 별표 17(식품접객업영업자 등의 준수사항, 제57조 관련) 전문</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>개정 2026.9.1</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>제7호 식품접객업자 준수사항에 영업신고증 비치·게시 의무 없음. 제9호 공유주방 운영업자는 영업등록증 보관 의무 있음. input/법령원문_261015/pdf5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>[접근 불가] 국가법령정보센터 웹(law.go.kr)·지자체 홈페이지</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>DNS 차단으로 직접 접속 불가. 모든 조문은 korean-law MCP(Open API)로 확인. 사용자 원문 재확인 권장 항목은 notes/questions.md 참조.</t>
         </is>
